--- a/Notas_N1_e_N2.xlsx
+++ b/Notas_N1_e_N2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\ano_2026S1\IA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8FD6C7D2-8592-4B5C-9F1D-F83F569F6062}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{300171CD-AF18-4244-8D6B-3647E69F786D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Notas B1" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Notas B1'!$A$1:$N$42</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Notas B2'!$A$1:$S$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Notas B2'!$A$1:$T$44</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="262">
   <si>
     <t>Nome</t>
   </si>
@@ -792,6 +792,42 @@
   </si>
   <si>
     <t>Alunos elegíveis a realizar a Substitutiva</t>
+  </si>
+  <si>
+    <t>10417401 ANNA LUIZA STELLA SANTOS 3,2</t>
+  </si>
+  <si>
+    <t>10416616 BEATRIZ LIMA DE MOURA 4,7</t>
+  </si>
+  <si>
+    <t>10418358 BRUNA AGUIAR MUCHIUTI 4,4</t>
+  </si>
+  <si>
+    <t>10417877 EDUARDO TAKASHI MISSAKA 5,1</t>
+  </si>
+  <si>
+    <t>10416751 GABRIEL TORTOLIO FONSECA 5,8</t>
+  </si>
+  <si>
+    <t>10417646 GIOVANA SIMOES FRANCO 4,9</t>
+  </si>
+  <si>
+    <t>10410870 ISMAEL DE SOUSA SILVA 5,2</t>
+  </si>
+  <si>
+    <t>10389419 LIVIA NEGRUCCI CANTOWITZ 3,7</t>
+  </si>
+  <si>
+    <t>10409051 MATHEUS HENRIQUE DE OLIVEIRA SANTOS 3,4</t>
+  </si>
+  <si>
+    <t>10418357 NICOLAS HENRIQUES DE ALMEIDA 5,2</t>
+  </si>
+  <si>
+    <t>10418118 THOMAS PINHEIRO GRANDIN 4,1</t>
+  </si>
+  <si>
+    <t>10410862 VITOR ALVES PEREIRA 4,8</t>
   </si>
 </sst>
 </file>
@@ -801,7 +837,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -853,6 +889,12 @@
       <family val="2"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF0070C0"/>
@@ -880,14 +922,27 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -922,7 +977,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
@@ -1042,63 +1097,79 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -3639,7 +3710,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{976B32EA-1F52-46D5-9E73-D7BC92A42345}">
-  <dimension ref="A1:W44"/>
+  <dimension ref="A1:X44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="44.85546875" bestFit="1" customWidth="1"/>
@@ -3649,19 +3720,20 @@
     <col min="7" max="7" width="9.140625" hidden="1" customWidth="1"/>
     <col min="8" max="8" width="4.85546875" style="57" customWidth="1"/>
     <col min="9" max="9" width="10.28515625" style="53" customWidth="1"/>
-    <col min="10" max="10" width="10.140625" style="66" customWidth="1"/>
-    <col min="11" max="11" width="10.140625" style="5" hidden="1" customWidth="1"/>
-    <col min="12" max="13" width="10.140625" style="69" customWidth="1"/>
-    <col min="14" max="14" width="1.42578125" style="71" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="31.7109375" style="70" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="8" style="57" customWidth="1"/>
-    <col min="19" max="19" width="9.140625" style="63"/>
-    <col min="20" max="20" width="7.85546875" style="5" customWidth="1"/>
-    <col min="21" max="21" width="13.42578125" style="5" customWidth="1"/>
-    <col min="22" max="22" width="5.85546875" style="5" customWidth="1"/>
+    <col min="10" max="10" width="10.28515625" style="80" customWidth="1"/>
+    <col min="11" max="11" width="10.140625" style="66" customWidth="1"/>
+    <col min="12" max="12" width="10.140625" style="5" hidden="1" customWidth="1"/>
+    <col min="13" max="14" width="10.140625" style="69" customWidth="1"/>
+    <col min="15" max="15" width="1.42578125" style="71" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="31.7109375" style="70" bestFit="1" customWidth="1"/>
+    <col min="17" max="19" width="8" style="57" customWidth="1"/>
+    <col min="20" max="20" width="9.140625" style="63"/>
+    <col min="21" max="21" width="7.85546875" style="5" customWidth="1"/>
+    <col min="22" max="22" width="13.42578125" style="5" customWidth="1"/>
+    <col min="23" max="23" width="5.85546875" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A1" s="26" t="s">
         <v>151</v>
       </c>
@@ -3689,46 +3761,49 @@
       <c r="I1" s="54" t="s">
         <v>213</v>
       </c>
-      <c r="J1" s="64" t="s">
+      <c r="J1" s="79" t="s">
+        <v>213</v>
+      </c>
+      <c r="K1" s="64" t="s">
         <v>211</v>
       </c>
-      <c r="K1" s="29" t="s">
+      <c r="L1" s="29" t="s">
         <v>212</v>
       </c>
-      <c r="L1" s="34" t="s">
+      <c r="M1" s="34" t="s">
         <v>210</v>
       </c>
-      <c r="M1" s="34" t="s">
+      <c r="N1" s="34" t="s">
         <v>200</v>
       </c>
-      <c r="N1" s="67" t="s">
+      <c r="O1" s="67" t="s">
         <v>201</v>
       </c>
-      <c r="O1" s="68" t="s">
+      <c r="P1" s="68" t="s">
         <v>207</v>
       </c>
-      <c r="P1" s="59" t="s">
+      <c r="Q1" s="59" t="s">
         <v>185</v>
       </c>
-      <c r="Q1" s="59" t="s">
+      <c r="R1" s="59" t="s">
         <v>184</v>
       </c>
-      <c r="R1" s="59" t="s">
+      <c r="S1" s="59" t="s">
         <v>186</v>
       </c>
-      <c r="S1" s="62"/>
-      <c r="T1" s="29" t="s">
+      <c r="T1" s="62"/>
+      <c r="U1" s="29" t="s">
         <v>206</v>
       </c>
-      <c r="U1" s="29" t="s">
+      <c r="V1" s="29" t="s">
         <v>208</v>
       </c>
-      <c r="V1" s="29" t="s">
+      <c r="W1" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="W1" s="33"/>
-    </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X1" s="33"/>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="str">
         <f>_xlfn.CONCAT(B2,"  ",C2)</f>
         <v>ALEX  KAZUO KODAMA</v>
@@ -3754,51 +3829,54 @@
       <c r="H2" s="57">
         <v>1</v>
       </c>
-      <c r="I2" s="53">
+      <c r="I2" s="75">
         <v>6</v>
       </c>
-      <c r="J2" s="53">
-        <f>_xlfn.CEILING.MATH(K2,0.5)</f>
-        <v>10</v>
-      </c>
-      <c r="K2" s="6">
-        <f>0.25*L2+0.75*M2</f>
-        <v>10</v>
-      </c>
-      <c r="L2" s="69">
-        <f>(T2+V2)/2</f>
+      <c r="J2" s="80">
+        <v>6</v>
+      </c>
+      <c r="K2" s="53">
+        <f>_xlfn.CEILING.MATH(L2,0.5)</f>
+        <v>10</v>
+      </c>
+      <c r="L2" s="6">
+        <f>0.25*M2+0.75*N2</f>
         <v>10</v>
       </c>
       <c r="M2" s="69">
+        <f>(U2+W2)/2</f>
         <v>10</v>
       </c>
       <c r="N2" s="69">
-        <f>SUM(P2,Q2,R2)</f>
-        <v>10</v>
-      </c>
-      <c r="O2" s="70" t="s">
+        <v>10</v>
+      </c>
+      <c r="O2" s="69">
+        <f>SUM(Q2,R2,S2)</f>
+        <v>10</v>
+      </c>
+      <c r="P2" s="70" t="s">
         <v>188</v>
       </c>
-      <c r="P2" s="57">
+      <c r="Q2" s="57">
         <v>3</v>
-      </c>
-      <c r="Q2" s="57">
-        <v>3.5</v>
       </c>
       <c r="R2" s="57">
         <v>3.5</v>
       </c>
-      <c r="S2" s="63" t="s">
+      <c r="S2" s="57">
+        <v>3.5</v>
+      </c>
+      <c r="T2" s="63" t="s">
         <v>187</v>
       </c>
-      <c r="T2" s="5">
-        <v>10</v>
-      </c>
-      <c r="V2" s="5">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="U2" s="5">
+        <v>10</v>
+      </c>
+      <c r="W2" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" s="41" t="str">
         <f>_xlfn.CONCAT(B3,"  ",C3)</f>
         <v>ANDRE  MOREIRA GUIMARAES</v>
@@ -3819,46 +3897,49 @@
         <v>7</v>
       </c>
       <c r="I3" s="65">
+        <v>10</v>
+      </c>
+      <c r="J3" s="81">
         <v>9</v>
       </c>
-      <c r="J3" s="53">
-        <f t="shared" ref="J3:J42" si="0">_xlfn.CEILING.MATH(K3,0.5)</f>
+      <c r="K3" s="53">
+        <f t="shared" ref="K3:K42" si="0">_xlfn.CEILING.MATH(L3,0.5)</f>
         <v>6.5</v>
       </c>
-      <c r="K3" s="6">
-        <f>0.25*L3+0.75*M3</f>
+      <c r="L3" s="6">
+        <f>0.25*M3+0.75*N3</f>
         <v>6.5</v>
       </c>
-      <c r="L3" s="69">
-        <f>(T3+V3)/2</f>
-        <v>5</v>
-      </c>
       <c r="M3" s="69">
+        <f>(U3+W3)/2</f>
+        <v>5</v>
+      </c>
+      <c r="N3" s="69">
         <v>7</v>
       </c>
-      <c r="N3" s="69">
-        <f>SUM(P3,Q3,R3)</f>
+      <c r="O3" s="69">
+        <f>SUM(Q3,R3,S3)</f>
         <v>7</v>
       </c>
-      <c r="O3" s="70" t="s">
+      <c r="P3" s="70" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="57">
+      <c r="Q3" s="57">
         <v>2</v>
-      </c>
-      <c r="Q3" s="57">
-        <v>2.5</v>
       </c>
       <c r="R3" s="57">
         <v>2.5</v>
       </c>
-      <c r="T3" s="44">
-        <v>10</v>
-      </c>
-      <c r="U3" s="44"/>
+      <c r="S3" s="57">
+        <v>2.5</v>
+      </c>
+      <c r="U3" s="44">
+        <v>10</v>
+      </c>
       <c r="V3" s="44"/>
-    </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W3" s="44"/>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="str">
         <f>_xlfn.CONCAT(B4,"  ",C4)</f>
         <v>ANNA  LUIZA STELLA SANTOS</v>
@@ -3883,25 +3964,28 @@
         <v>2</v>
       </c>
       <c r="I4" s="53">
+        <v>5</v>
+      </c>
+      <c r="J4" s="80">
         <v>4</v>
       </c>
-      <c r="J4" s="53">
+      <c r="K4" s="53">
         <f t="shared" si="0"/>
         <v>1.5</v>
       </c>
-      <c r="K4" s="6">
-        <f>0.25*L4+0.75*M4</f>
+      <c r="L4" s="6">
+        <f>0.25*M4+0.75*N4</f>
         <v>1.25</v>
       </c>
-      <c r="L4" s="69">
-        <f>(T4+V4)/2</f>
-        <v>5</v>
-      </c>
-      <c r="T4" s="5">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="M4" s="69">
+        <f>(U4+W4)/2</f>
+        <v>5</v>
+      </c>
+      <c r="U4" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" s="18" t="str">
         <f>_xlfn.CONCAT(B5,"  ",C5)</f>
         <v>BEATRIZ  LIMA DE MOURA</v>
@@ -3926,52 +4010,55 @@
         <v>3</v>
       </c>
       <c r="I5" s="54">
+        <v>5.5</v>
+      </c>
+      <c r="J5" s="79">
         <v>4.5</v>
       </c>
-      <c r="J5" s="54">
+      <c r="K5" s="54">
         <f t="shared" si="0"/>
         <v>9.5</v>
       </c>
-      <c r="K5" s="55">
-        <f>0.25*L5+0.75*M5</f>
+      <c r="L5" s="55">
+        <f>0.25*M5+0.75*N5</f>
         <v>9.125</v>
       </c>
-      <c r="L5" s="72">
-        <f>(T5+V5)/2</f>
+      <c r="M5" s="72">
+        <f>(U5+W5)/2</f>
         <v>9.5</v>
       </c>
-      <c r="M5" s="72">
+      <c r="N5" s="72">
         <v>9</v>
       </c>
-      <c r="N5" s="72">
-        <f>SUM(P5,Q5,R5)</f>
+      <c r="O5" s="72">
+        <f>SUM(Q5,R5,S5)</f>
         <v>9</v>
       </c>
-      <c r="O5" s="73" t="s">
+      <c r="P5" s="73" t="s">
         <v>189</v>
       </c>
-      <c r="P5" s="59">
+      <c r="Q5" s="59">
         <v>3</v>
       </c>
-      <c r="Q5" s="59">
+      <c r="R5" s="59">
         <v>3.5</v>
       </c>
-      <c r="R5" s="59">
+      <c r="S5" s="59">
         <v>2.5</v>
       </c>
-      <c r="S5" s="62" t="s">
+      <c r="T5" s="62" t="s">
         <v>197</v>
       </c>
-      <c r="T5" s="22">
-        <v>10</v>
-      </c>
-      <c r="U5" s="22"/>
-      <c r="V5" s="22">
+      <c r="U5" s="22">
+        <v>10</v>
+      </c>
+      <c r="V5" s="22"/>
+      <c r="W5" s="22">
         <v>9</v>
       </c>
-      <c r="W5" s="33"/>
-    </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X5" s="33"/>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="str">
         <f>_xlfn.CONCAT(B6,"  ",C6)</f>
         <v>BERNARDO  SOUZA OLIVEIRA</v>
@@ -3996,36 +4083,39 @@
         <v>7</v>
       </c>
       <c r="I6" s="53">
+        <v>9.5</v>
+      </c>
+      <c r="J6" s="80">
         <v>8.5</v>
       </c>
-      <c r="J6" s="53">
+      <c r="K6" s="53">
         <f t="shared" si="0"/>
         <v>7.5</v>
       </c>
-      <c r="K6" s="6">
-        <f>0.25*L6+0.75*M6</f>
+      <c r="L6" s="6">
+        <f>0.25*M6+0.75*N6</f>
         <v>7.25</v>
       </c>
-      <c r="L6" s="69">
-        <f>(T6+V6)/2</f>
+      <c r="M6" s="69">
+        <f>(U6+W6)/2</f>
         <v>8</v>
       </c>
-      <c r="M6" s="69">
+      <c r="N6" s="69">
         <v>7</v>
       </c>
-      <c r="N6" s="69">
-        <f>N5</f>
+      <c r="O6" s="69">
+        <f>O5</f>
         <v>9</v>
       </c>
-      <c r="T6" s="11" t="s">
+      <c r="U6" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="U6" s="11"/>
-      <c r="V6" s="51" t="s">
+      <c r="V6" s="11"/>
+      <c r="W6" s="51" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="str">
         <f>_xlfn.CONCAT(B7,"  ",C7)</f>
         <v>BRUNA  AGUIAR MUCHIUTI</v>
@@ -4050,47 +4140,50 @@
         <v>9</v>
       </c>
       <c r="I7" s="53">
+        <v>5</v>
+      </c>
+      <c r="J7" s="80">
         <v>4</v>
       </c>
-      <c r="J7" s="53">
+      <c r="K7" s="53">
         <f t="shared" si="0"/>
         <v>7.5</v>
       </c>
-      <c r="K7" s="6">
-        <f>0.25*L7+0.75*M7</f>
+      <c r="L7" s="6">
+        <f>0.25*M7+0.75*N7</f>
         <v>7.375</v>
       </c>
-      <c r="L7" s="69">
-        <f>(T7+V7)/2</f>
-        <v>10</v>
-      </c>
       <c r="M7" s="69">
+        <f>(U7+W7)/2</f>
+        <v>10</v>
+      </c>
+      <c r="N7" s="69">
         <v>6.5</v>
       </c>
-      <c r="N7" s="69">
-        <f>SUM(P7,Q7,R7)</f>
+      <c r="O7" s="69">
+        <f>SUM(Q7,R7,S7)</f>
         <v>6.5</v>
       </c>
-      <c r="O7" s="70" t="s">
+      <c r="P7" s="70" t="s">
         <v>194</v>
       </c>
-      <c r="P7" s="57">
+      <c r="Q7" s="57">
         <v>1.5</v>
-      </c>
-      <c r="Q7" s="57">
-        <v>2.5</v>
       </c>
       <c r="R7" s="57">
         <v>2.5</v>
       </c>
-      <c r="T7" s="5">
-        <v>10</v>
-      </c>
-      <c r="V7" s="5">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="S7" s="57">
+        <v>2.5</v>
+      </c>
+      <c r="U7" s="5">
+        <v>10</v>
+      </c>
+      <c r="W7" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="str">
         <f>_xlfn.CONCAT(B8,"  ",C8)</f>
         <v>BRUNO  ANTICO GALIN</v>
@@ -4115,32 +4208,32 @@
         <v>4</v>
       </c>
       <c r="I8" s="53">
+        <v>6.5</v>
+      </c>
+      <c r="J8" s="80">
         <v>5.5</v>
       </c>
-      <c r="J8" s="53">
+      <c r="K8" s="53">
         <f t="shared" si="0"/>
         <v>8.5</v>
       </c>
-      <c r="K8" s="6">
-        <f>0.25*L8+0.75*M8</f>
+      <c r="L8" s="6">
+        <f>0.25*M8+0.75*N8</f>
         <v>8.125</v>
       </c>
-      <c r="L8" s="69">
-        <f>(T8+V8)/2</f>
-        <v>10</v>
-      </c>
       <c r="M8" s="69">
+        <f>(U8+W8)/2</f>
+        <v>10</v>
+      </c>
+      <c r="N8" s="69">
         <v>7.5</v>
       </c>
-      <c r="N8" s="69">
-        <f>SUM(P8,Q8,R8)</f>
+      <c r="O8" s="69">
+        <f>SUM(Q8,R8,S8)</f>
         <v>7.5</v>
       </c>
-      <c r="O8" s="70" t="s">
+      <c r="P8" s="70" t="s">
         <v>193</v>
-      </c>
-      <c r="P8" s="57">
-        <v>2.5</v>
       </c>
       <c r="Q8" s="57">
         <v>2.5</v>
@@ -4148,14 +4241,17 @@
       <c r="R8" s="57">
         <v>2.5</v>
       </c>
-      <c r="T8" s="5">
-        <v>10</v>
-      </c>
-      <c r="V8" s="5">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="S8" s="57">
+        <v>2.5</v>
+      </c>
+      <c r="U8" s="5">
+        <v>10</v>
+      </c>
+      <c r="W8" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="str">
         <f>_xlfn.CONCAT(B9,"  ",C9)</f>
         <v>BRUNO  LAUAND FERRAO</v>
@@ -4180,50 +4276,53 @@
         <v>5</v>
       </c>
       <c r="I9" s="53">
+        <v>5.5</v>
+      </c>
+      <c r="J9" s="80">
         <v>4.5</v>
       </c>
-      <c r="J9" s="53">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="K9" s="6">
-        <f>0.25*L9+0.75*M9</f>
+      <c r="K9" s="53">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="L9" s="6">
+        <f>0.25*M9+0.75*N9</f>
         <v>9.875</v>
       </c>
-      <c r="L9" s="69">
-        <f>(T9+V9)/2</f>
+      <c r="M9" s="69">
+        <f>(U9+W9)/2</f>
         <v>9.5</v>
       </c>
-      <c r="M9" s="69">
-        <v>10</v>
-      </c>
       <c r="N9" s="69">
-        <f>SUM(P9,Q9,R9)</f>
-        <v>10</v>
-      </c>
-      <c r="O9" s="70" t="s">
+        <v>10</v>
+      </c>
+      <c r="O9" s="69">
+        <f>SUM(Q9,R9,S9)</f>
+        <v>10</v>
+      </c>
+      <c r="P9" s="70" t="s">
         <v>192</v>
       </c>
-      <c r="P9" s="57">
+      <c r="Q9" s="57">
         <v>3</v>
-      </c>
-      <c r="Q9" s="57">
-        <v>3.5</v>
       </c>
       <c r="R9" s="57">
         <v>3.5</v>
       </c>
-      <c r="S9" s="63" t="s">
+      <c r="S9" s="57">
+        <v>3.5</v>
+      </c>
+      <c r="T9" s="63" t="s">
         <v>198</v>
       </c>
-      <c r="T9" s="5">
-        <v>10</v>
-      </c>
-      <c r="V9" s="5">
+      <c r="U9" s="5">
+        <v>10</v>
+      </c>
+      <c r="W9" s="5">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" s="18" t="str">
         <f>_xlfn.CONCAT(B10,"  ",C10)</f>
         <v>CAUE  MACEDO DE SOUZA</v>
@@ -4241,34 +4340,37 @@
       <c r="F10" s="20"/>
       <c r="G10" s="21"/>
       <c r="H10" s="59"/>
-      <c r="I10" s="54">
+      <c r="I10" s="76">
         <v>3</v>
       </c>
-      <c r="J10" s="54">
+      <c r="J10" s="79">
+        <v>3</v>
+      </c>
+      <c r="K10" s="54">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K10" s="55">
-        <f>0.25*L10+0.75*M10</f>
+      <c r="L10" s="55">
+        <f>0.25*M10+0.75*N10</f>
         <v>0</v>
       </c>
-      <c r="L10" s="72">
-        <f>(T10+V10)/2</f>
+      <c r="M10" s="72">
+        <f>(U10+W10)/2</f>
         <v>0</v>
       </c>
-      <c r="M10" s="72"/>
       <c r="N10" s="72"/>
-      <c r="O10" s="73"/>
-      <c r="P10" s="59"/>
+      <c r="O10" s="72"/>
+      <c r="P10" s="73"/>
       <c r="Q10" s="59"/>
       <c r="R10" s="59"/>
-      <c r="S10" s="62"/>
-      <c r="T10" s="22"/>
+      <c r="S10" s="59"/>
+      <c r="T10" s="62"/>
       <c r="U10" s="22"/>
       <c r="V10" s="22"/>
-      <c r="W10" s="33"/>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W10" s="22"/>
+      <c r="X10" s="33"/>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="str">
         <f>_xlfn.CONCAT(B11,"  ",C11)</f>
         <v>CLEVERSON  PEREIRA DA SILVA</v>
@@ -4293,36 +4395,38 @@
         <v>4</v>
       </c>
       <c r="I11" s="53">
+        <v>4</v>
+      </c>
+      <c r="J11" s="80">
         <v>3</v>
       </c>
-      <c r="J11" s="53">
-        <f t="shared" si="0"/>
-        <v>8.5</v>
-      </c>
-      <c r="K11" s="6">
-        <f>0.25*L11+0.75*M11</f>
-        <v>8.125</v>
-      </c>
-      <c r="L11" s="69">
-        <f>(T11+V11)/2</f>
-        <v>10</v>
+      <c r="K11" s="53">
+        <f t="shared" si="0"/>
+        <v>7.5</v>
+      </c>
+      <c r="L11" s="6">
+        <f>0.25*M11+0.75*N11</f>
+        <v>7.375</v>
       </c>
       <c r="M11" s="69">
+        <v>7</v>
+      </c>
+      <c r="N11" s="69">
         <v>7.5</v>
       </c>
-      <c r="N11" s="69">
-        <f>N10</f>
+      <c r="O11" s="69">
+        <f>O10</f>
         <v>0</v>
       </c>
-      <c r="T11" s="11" t="s">
+      <c r="U11" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="U11" s="11"/>
-      <c r="V11" s="51" t="s">
+      <c r="V11" s="11"/>
+      <c r="W11" s="51" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="str">
         <f>_xlfn.CONCAT(B12,"  ",C12)</f>
         <v>EDUARDO  OLIVEIRA CARVALHO</v>
@@ -4347,44 +4451,47 @@
         <v>6</v>
       </c>
       <c r="I12" s="53">
+        <v>8</v>
+      </c>
+      <c r="J12" s="80">
         <v>7</v>
       </c>
-      <c r="J12" s="53">
+      <c r="K12" s="53">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="K12" s="6">
-        <f>0.25*L12+0.75*M12</f>
+      <c r="L12" s="6">
+        <f>0.25*M12+0.75*N12</f>
         <v>5.75</v>
       </c>
-      <c r="L12" s="69">
-        <f>(T12+V12)/2</f>
-        <v>5</v>
-      </c>
       <c r="M12" s="69">
+        <f>(U12+W12)/2</f>
+        <v>5</v>
+      </c>
+      <c r="N12" s="69">
         <v>6</v>
       </c>
-      <c r="N12" s="69">
-        <f>SUM(P12,Q12,R12)</f>
+      <c r="O12" s="69">
+        <f>SUM(Q12,R12,S12)</f>
         <v>6</v>
       </c>
-      <c r="O12" s="70" t="s">
+      <c r="P12" s="70" t="s">
         <v>196</v>
       </c>
-      <c r="P12" s="57">
+      <c r="Q12" s="57">
         <v>1.5</v>
       </c>
-      <c r="Q12" s="57">
+      <c r="R12" s="57">
         <v>2.5</v>
       </c>
-      <c r="R12" s="57">
+      <c r="S12" s="57">
         <v>2</v>
       </c>
-      <c r="V12" s="5">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W12" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" s="41" t="str">
         <f>_xlfn.CONCAT(B13,"  ",C13)</f>
         <v>EDUARDO  TAKASHI MISSAKA</v>
@@ -4409,36 +4516,39 @@
         <v>4</v>
       </c>
       <c r="I13" s="65">
+        <v>5</v>
+      </c>
+      <c r="J13" s="81">
         <v>4</v>
       </c>
-      <c r="J13" s="53">
+      <c r="K13" s="53">
         <f t="shared" si="0"/>
         <v>8.5</v>
       </c>
-      <c r="K13" s="6">
-        <f>0.25*L13+0.75*M13</f>
+      <c r="L13" s="6">
+        <f>0.25*M13+0.75*N13</f>
         <v>8.125</v>
       </c>
-      <c r="L13" s="69">
-        <f>(T13+V13)/2</f>
-        <v>10</v>
-      </c>
       <c r="M13" s="69">
+        <f>(U13+W13)/2</f>
+        <v>10</v>
+      </c>
+      <c r="N13" s="69">
         <v>7.5</v>
       </c>
-      <c r="N13" s="69">
-        <f>N12</f>
+      <c r="O13" s="69">
+        <f>O12</f>
         <v>6</v>
       </c>
-      <c r="T13" s="44">
-        <v>10</v>
-      </c>
-      <c r="U13" s="44"/>
-      <c r="V13" s="44">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="U13" s="44">
+        <v>10</v>
+      </c>
+      <c r="V13" s="44"/>
+      <c r="W13" s="44">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="str">
         <f>_xlfn.CONCAT(B14,"  ",C14)</f>
         <v>ENZO  BENEDETTO PROENCA</v>
@@ -4463,35 +4573,38 @@
         <v>9</v>
       </c>
       <c r="I14" s="53">
+        <v>7</v>
+      </c>
+      <c r="J14" s="80">
         <v>6</v>
       </c>
-      <c r="J14" s="53">
+      <c r="K14" s="53">
         <f t="shared" si="0"/>
         <v>7.5</v>
       </c>
-      <c r="K14" s="6">
-        <f>0.25*L14+0.75*M14</f>
+      <c r="L14" s="6">
+        <f>0.25*M14+0.75*N14</f>
         <v>7.375</v>
       </c>
-      <c r="L14" s="69">
-        <f>(T14+V14)/2</f>
-        <v>10</v>
-      </c>
       <c r="M14" s="69">
+        <f>(U14+W14)/2</f>
+        <v>10</v>
+      </c>
+      <c r="N14" s="69">
         <v>6.5</v>
       </c>
-      <c r="N14" s="69">
-        <f>N13</f>
+      <c r="O14" s="69">
+        <f>O13</f>
         <v>6</v>
       </c>
-      <c r="T14" s="5">
-        <v>10</v>
-      </c>
-      <c r="V14" s="5">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="U14" s="5">
+        <v>10</v>
+      </c>
+      <c r="W14" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="str">
         <f>_xlfn.CONCAT(B15,"  ",C15)</f>
         <v>FELIPE  VIVIANI SCHULZE</v>
@@ -4515,43 +4628,46 @@
       <c r="H15" s="59">
         <v>6</v>
       </c>
-      <c r="I15" s="54">
+      <c r="I15" s="76">
         <v>6.5</v>
       </c>
-      <c r="J15" s="54">
+      <c r="J15" s="79">
+        <v>6.5</v>
+      </c>
+      <c r="K15" s="54">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="K15" s="55">
-        <f>0.25*L15+0.75*M15</f>
+      <c r="L15" s="55">
+        <f>0.25*M15+0.75*N15</f>
         <v>7</v>
       </c>
-      <c r="L15" s="72">
-        <f>(T15+V15)/2</f>
-        <v>10</v>
-      </c>
       <c r="M15" s="72">
+        <f>(U15+W15)/2</f>
+        <v>10</v>
+      </c>
+      <c r="N15" s="72">
         <v>6</v>
       </c>
-      <c r="N15" s="72">
-        <f>N14</f>
+      <c r="O15" s="72">
+        <f>O14</f>
         <v>6</v>
       </c>
-      <c r="O15" s="73"/>
-      <c r="P15" s="59"/>
+      <c r="P15" s="73"/>
       <c r="Q15" s="59"/>
       <c r="R15" s="59"/>
-      <c r="S15" s="62"/>
-      <c r="T15" s="22">
-        <v>10</v>
-      </c>
-      <c r="U15" s="22"/>
-      <c r="V15" s="22">
-        <v>10</v>
-      </c>
-      <c r="W15" s="33"/>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="S15" s="59"/>
+      <c r="T15" s="62"/>
+      <c r="U15" s="22">
+        <v>10</v>
+      </c>
+      <c r="V15" s="22"/>
+      <c r="W15" s="22">
+        <v>10</v>
+      </c>
+      <c r="X15" s="33"/>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="str">
         <f>_xlfn.CONCAT(B16,"  ",C16)</f>
         <v>FERNANDO  MATHIAS FERRO DOS SANTOS</v>
@@ -4575,37 +4691,40 @@
       <c r="H16" s="60">
         <v>6</v>
       </c>
-      <c r="I16" s="53">
+      <c r="I16" s="75">
+        <v>5</v>
+      </c>
+      <c r="J16" s="80">
         <v>4</v>
       </c>
-      <c r="J16" s="53">
+      <c r="K16" s="53">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="K16" s="6">
-        <f>0.25*L16+0.75*M16</f>
+      <c r="L16" s="6">
+        <f>0.25*M16+0.75*N16</f>
         <v>7</v>
       </c>
-      <c r="L16" s="69">
-        <f>(T16+V16)/2</f>
-        <v>10</v>
-      </c>
       <c r="M16" s="69">
+        <f>(U16+W16)/2</f>
+        <v>10</v>
+      </c>
+      <c r="N16" s="69">
         <v>6</v>
       </c>
-      <c r="N16" s="69">
-        <f>N15</f>
+      <c r="O16" s="69">
+        <f>O15</f>
         <v>6</v>
       </c>
-      <c r="T16" s="11" t="s">
+      <c r="U16" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="U16" s="11"/>
-      <c r="V16" s="51" t="s">
+      <c r="V16" s="11"/>
+      <c r="W16" s="51" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="str">
         <f>_xlfn.CONCAT(B17,"  ",C17)</f>
         <v>FRANCISCO  LOSADA TOTARO</v>
@@ -4629,36 +4748,39 @@
       <c r="H17" s="57">
         <v>6</v>
       </c>
-      <c r="I17" s="53">
+      <c r="I17" s="75">
         <v>4.5</v>
       </c>
-      <c r="J17" s="53">
+      <c r="J17" s="80">
+        <v>4.5</v>
+      </c>
+      <c r="K17" s="53">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="K17" s="6">
-        <f>0.25*L17+0.75*M17</f>
+      <c r="L17" s="6">
+        <f>0.25*M17+0.75*N17</f>
         <v>7</v>
       </c>
-      <c r="L17" s="69">
-        <f>(T17+V17)/2</f>
-        <v>10</v>
-      </c>
       <c r="M17" s="69">
+        <f>(U17+W17)/2</f>
+        <v>10</v>
+      </c>
+      <c r="N17" s="69">
         <v>6</v>
       </c>
-      <c r="N17" s="69">
-        <f>N16</f>
+      <c r="O17" s="69">
+        <f>O16</f>
         <v>6</v>
       </c>
-      <c r="T17" s="5">
-        <v>10</v>
-      </c>
-      <c r="V17" s="5">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="U17" s="5">
+        <v>10</v>
+      </c>
+      <c r="W17" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="str">
         <f>_xlfn.CONCAT(B18,"  ",C18)</f>
         <v>GABRIEL  KEN KAZAMA GERONAZZO</v>
@@ -4683,35 +4805,38 @@
         <v>9</v>
       </c>
       <c r="I18" s="53">
+        <v>9</v>
+      </c>
+      <c r="J18" s="80">
         <v>8</v>
       </c>
-      <c r="J18" s="53">
+      <c r="K18" s="53">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="K18" s="6">
-        <f>0.25*L18+0.75*M18</f>
+      <c r="L18" s="6">
+        <f>0.25*M18+0.75*N18</f>
         <v>6.75</v>
       </c>
-      <c r="L18" s="69">
-        <f>(T18+V18)/2</f>
+      <c r="M18" s="69">
+        <f>(U18+W18)/2</f>
         <v>7.5</v>
       </c>
-      <c r="M18" s="69">
+      <c r="N18" s="69">
         <v>6.5</v>
       </c>
-      <c r="N18" s="69">
-        <f>N17</f>
+      <c r="O18" s="69">
+        <f>O17</f>
         <v>6</v>
       </c>
-      <c r="T18" s="5">
-        <v>10</v>
-      </c>
-      <c r="V18" s="5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="U18" s="5">
+        <v>10</v>
+      </c>
+      <c r="W18" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" s="41" t="str">
         <f>_xlfn.CONCAT(B19,"  ",C19)</f>
         <v>GABRIEL  LAZARETI CARDOSO</v>
@@ -4731,46 +4856,49 @@
       <c r="H19" s="58">
         <v>8</v>
       </c>
-      <c r="I19" s="65"/>
-      <c r="J19" s="53">
+      <c r="I19" s="65" t="s">
+        <v>8</v>
+      </c>
+      <c r="J19" s="81"/>
+      <c r="K19" s="53">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="K19" s="6">
-        <f>0.25*L19+0.75*M19</f>
+      <c r="L19" s="6">
+        <f>0.25*M19+0.75*N19</f>
         <v>6</v>
       </c>
-      <c r="L19" s="69">
-        <f>(T19+V19)/2</f>
+      <c r="M19" s="69">
+        <f>(U19+W19)/2</f>
         <v>0</v>
       </c>
-      <c r="M19" s="69">
+      <c r="N19" s="69">
         <v>8</v>
       </c>
-      <c r="N19" s="69">
-        <f>SUM(P19,Q19,R19)</f>
+      <c r="O19" s="69">
+        <f>SUM(Q19,R19,S19)</f>
         <v>8</v>
       </c>
-      <c r="O19" s="70" t="s">
+      <c r="P19" s="70" t="s">
         <v>195</v>
       </c>
-      <c r="P19" s="57">
+      <c r="Q19" s="57">
         <v>2.5</v>
       </c>
-      <c r="Q19" s="57">
+      <c r="R19" s="57">
         <v>3</v>
       </c>
-      <c r="R19" s="57">
+      <c r="S19" s="57">
         <v>2.5</v>
       </c>
-      <c r="S19" s="63" t="s">
+      <c r="T19" s="63" t="s">
         <v>199</v>
       </c>
-      <c r="T19" s="44"/>
       <c r="U19" s="44"/>
       <c r="V19" s="44"/>
-    </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W19" s="44"/>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" s="18" t="str">
         <f>_xlfn.CONCAT(B20,"  ",C20)</f>
         <v>GABRIEL  TORTOLIO FONSECA</v>
@@ -4791,42 +4919,45 @@
         <v>1</v>
       </c>
       <c r="I20" s="54">
+        <v>4</v>
+      </c>
+      <c r="J20" s="79">
         <v>3</v>
       </c>
-      <c r="J20" s="54">
+      <c r="K20" s="54">
         <f t="shared" si="0"/>
         <v>8.5</v>
       </c>
-      <c r="K20" s="55">
-        <f>0.25*L20+0.75*M20</f>
+      <c r="L20" s="55">
+        <f>0.25*M20+0.75*N20</f>
         <v>8.375</v>
       </c>
-      <c r="L20" s="72">
-        <f>(T20+V20)/2</f>
+      <c r="M20" s="72">
+        <f>(U20+W20)/2</f>
         <v>3.5</v>
       </c>
-      <c r="M20" s="72">
-        <v>10</v>
-      </c>
       <c r="N20" s="72">
-        <f>N19</f>
+        <v>10</v>
+      </c>
+      <c r="O20" s="72">
+        <f>O19</f>
         <v>8</v>
       </c>
-      <c r="O20" s="73"/>
-      <c r="P20" s="59"/>
+      <c r="P20" s="73"/>
       <c r="Q20" s="59"/>
       <c r="R20" s="59"/>
-      <c r="S20" s="62"/>
-      <c r="T20" s="22">
+      <c r="S20" s="59"/>
+      <c r="T20" s="62"/>
+      <c r="U20" s="22">
         <v>7</v>
       </c>
-      <c r="U20" s="22" t="s">
+      <c r="V20" s="22" t="s">
         <v>203</v>
       </c>
-      <c r="V20" s="22"/>
-      <c r="W20" s="33"/>
-    </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W20" s="22"/>
+      <c r="X20" s="33"/>
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21" s="41" t="str">
         <f>_xlfn.CONCAT(B21,"  ",C21)</f>
         <v>GIOVANA  SIMOES FRANCO</v>
@@ -4851,36 +4982,39 @@
         <v>3</v>
       </c>
       <c r="I21" s="65">
+        <v>7</v>
+      </c>
+      <c r="J21" s="81">
         <v>6</v>
       </c>
-      <c r="J21" s="53">
+      <c r="K21" s="53">
         <f t="shared" si="0"/>
         <v>9.5</v>
       </c>
-      <c r="K21" s="6">
-        <f>0.25*L21+0.75*M21</f>
+      <c r="L21" s="6">
+        <f>0.25*M21+0.75*N21</f>
         <v>9.25</v>
       </c>
-      <c r="L21" s="69">
-        <f>(T21+V21)/2</f>
-        <v>10</v>
-      </c>
       <c r="M21" s="69">
+        <f>(U21+W21)/2</f>
+        <v>10</v>
+      </c>
+      <c r="N21" s="69">
         <v>9</v>
       </c>
-      <c r="N21" s="69">
-        <f>N20</f>
+      <c r="O21" s="69">
+        <f>O20</f>
         <v>8</v>
       </c>
-      <c r="T21" s="48" t="s">
+      <c r="U21" s="48" t="s">
         <v>202</v>
       </c>
-      <c r="U21" s="48"/>
-      <c r="V21" s="52" t="s">
+      <c r="V21" s="48"/>
+      <c r="W21" s="52" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="str">
         <f>_xlfn.CONCAT(B22,"  ",C22)</f>
         <v>GUILHERME  FERREIRA MARTINS RAMOS</v>
@@ -4905,32 +5039,35 @@
         <v>6</v>
       </c>
       <c r="I22" s="53">
+        <v>8</v>
+      </c>
+      <c r="J22" s="80">
         <v>7</v>
       </c>
-      <c r="J22" s="53">
+      <c r="K22" s="53">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="K22" s="6">
-        <f>0.25*L22+0.75*M22</f>
+      <c r="L22" s="6">
+        <f>0.25*M22+0.75*N22</f>
         <v>5.75</v>
       </c>
-      <c r="L22" s="69">
-        <f>(T22+V22)/2</f>
-        <v>5</v>
-      </c>
       <c r="M22" s="69">
+        <f>(U22+W22)/2</f>
+        <v>5</v>
+      </c>
+      <c r="N22" s="69">
         <v>6</v>
       </c>
-      <c r="N22" s="69">
-        <f>N21</f>
+      <c r="O22" s="69">
+        <f>O21</f>
         <v>8</v>
       </c>
-      <c r="V22" s="5">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W22" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="str">
         <f>_xlfn.CONCAT(B23,"  ",C23)</f>
         <v>GUSTAVO  KENZO NAKAZATO SLEIMAN</v>
@@ -4945,20 +5082,23 @@
       <c r="E23" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="J23" s="53">
+      <c r="I23" s="53" t="s">
+        <v>8</v>
+      </c>
+      <c r="K23" s="53">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K23" s="6">
-        <f>0.25*L23+0.75*M23</f>
+      <c r="L23" s="6">
+        <f>0.25*M23+0.75*N23</f>
         <v>0</v>
       </c>
-      <c r="L23" s="69">
-        <f>(T23+V23)/2</f>
+      <c r="M23" s="69">
+        <f>(U23+W23)/2</f>
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="str">
         <f>_xlfn.CONCAT(B24,"  ",C24)</f>
         <v>HENRIQUE  YUJI ISOGAI YONEOKA</v>
@@ -4982,37 +5122,40 @@
       <c r="H24" s="57">
         <v>7</v>
       </c>
-      <c r="I24" s="53">
+      <c r="I24" s="75">
         <v>4</v>
       </c>
-      <c r="J24" s="53">
+      <c r="J24" s="80">
+        <v>4</v>
+      </c>
+      <c r="K24" s="53">
         <f t="shared" si="0"/>
         <v>6.5</v>
       </c>
-      <c r="K24" s="6">
-        <f>0.25*L24+0.75*M24</f>
+      <c r="L24" s="6">
+        <f>0.25*M24+0.75*N24</f>
         <v>6.125</v>
       </c>
-      <c r="L24" s="69">
-        <f>(T24+V24)/2</f>
+      <c r="M24" s="69">
+        <f>(U24+W24)/2</f>
         <v>3.5</v>
       </c>
-      <c r="M24" s="69">
+      <c r="N24" s="69">
         <v>7</v>
       </c>
-      <c r="N24" s="69">
-        <f>N23</f>
+      <c r="O24" s="69">
+        <f>O23</f>
         <v>0</v>
       </c>
-      <c r="T24" s="5">
+      <c r="U24" s="5">
         <v>7</v>
       </c>
-      <c r="U24" s="50" t="s">
+      <c r="V24" s="50" t="s">
         <v>204</v>
       </c>
-      <c r="V24" s="50"/>
-    </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W24" s="50"/>
+    </row>
+    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A25" s="18" t="str">
         <f>_xlfn.CONCAT(B25,"  ",C25)</f>
         <v>ISMAEL  DE SOUSA SILVA</v>
@@ -5037,42 +5180,45 @@
         <v>4</v>
       </c>
       <c r="I25" s="54">
-        <v>5</v>
-      </c>
-      <c r="J25" s="54">
+        <v>6</v>
+      </c>
+      <c r="J25" s="79">
+        <v>5</v>
+      </c>
+      <c r="K25" s="54">
         <f t="shared" si="0"/>
         <v>8.5</v>
       </c>
-      <c r="K25" s="55">
-        <f>0.25*L25+0.75*M25</f>
+      <c r="L25" s="55">
+        <f>0.25*M25+0.75*N25</f>
         <v>8.125</v>
       </c>
-      <c r="L25" s="72">
-        <f>(T25+V25)/2</f>
-        <v>10</v>
-      </c>
       <c r="M25" s="72">
+        <f>(U25+W25)/2</f>
+        <v>10</v>
+      </c>
+      <c r="N25" s="72">
         <v>7.5</v>
       </c>
-      <c r="N25" s="72">
-        <f>N24</f>
+      <c r="O25" s="72">
+        <f>O24</f>
         <v>0</v>
       </c>
-      <c r="O25" s="73"/>
-      <c r="P25" s="59"/>
+      <c r="P25" s="73"/>
       <c r="Q25" s="59"/>
       <c r="R25" s="59"/>
-      <c r="S25" s="62"/>
-      <c r="T25" s="22">
-        <v>10</v>
-      </c>
-      <c r="U25" s="22"/>
-      <c r="V25" s="22">
-        <v>10</v>
-      </c>
-      <c r="W25" s="33"/>
-    </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="S25" s="59"/>
+      <c r="T25" s="62"/>
+      <c r="U25" s="22">
+        <v>10</v>
+      </c>
+      <c r="V25" s="22"/>
+      <c r="W25" s="22">
+        <v>10</v>
+      </c>
+      <c r="X25" s="33"/>
+    </row>
+    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="str">
         <f>_xlfn.CONCAT(B26,"  ",C26)</f>
         <v>JESSICA  DOS SANTOS SANTANA BISPO</v>
@@ -5097,36 +5243,39 @@
         <v>9</v>
       </c>
       <c r="I26" s="53">
+        <v>5.5</v>
+      </c>
+      <c r="J26" s="80">
         <v>4.5</v>
       </c>
-      <c r="J26" s="53">
+      <c r="K26" s="53">
         <f t="shared" si="0"/>
         <v>7.5</v>
       </c>
-      <c r="K26" s="6">
-        <f>0.25*L26+0.75*M26</f>
+      <c r="L26" s="6">
+        <f>0.25*M26+0.75*N26</f>
         <v>7.375</v>
       </c>
-      <c r="L26" s="69">
-        <f>(T26+V26)/2</f>
-        <v>10</v>
-      </c>
       <c r="M26" s="69">
+        <f>(U26+W26)/2</f>
+        <v>10</v>
+      </c>
+      <c r="N26" s="69">
         <v>6.5</v>
       </c>
-      <c r="N26" s="69">
-        <f>N25</f>
+      <c r="O26" s="69">
+        <f>O25</f>
         <v>0</v>
       </c>
-      <c r="T26" s="11" t="s">
+      <c r="U26" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="U26" s="11"/>
-      <c r="V26" s="51" t="s">
+      <c r="V26" s="11"/>
+      <c r="W26" s="51" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="str">
         <f>_xlfn.CONCAT(B27,"  ",C27)</f>
         <v>JOAO  ROCHA MURGEL</v>
@@ -5145,30 +5294,30 @@
       <c r="H27" s="57">
         <v>8</v>
       </c>
-      <c r="J27" s="53">
+      <c r="K27" s="53">
         <f t="shared" si="0"/>
         <v>7.5</v>
       </c>
-      <c r="K27" s="6">
-        <f>0.25*L27+0.75*M27</f>
+      <c r="L27" s="6">
+        <f>0.25*M27+0.75*N27</f>
         <v>7.25</v>
       </c>
-      <c r="L27" s="69">
-        <f>(T27+V27)/2</f>
-        <v>5</v>
-      </c>
       <c r="M27" s="69">
+        <f>(U27+W27)/2</f>
+        <v>5</v>
+      </c>
+      <c r="N27" s="69">
         <v>8</v>
       </c>
-      <c r="N27" s="69">
-        <f>N26</f>
+      <c r="O27" s="69">
+        <f>O26</f>
         <v>0</v>
       </c>
-      <c r="T27" s="5">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="U27" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="str">
         <f>_xlfn.CONCAT(B28,"  ",C28)</f>
         <v>JOAO  VICTOR MARTINS</v>
@@ -5186,33 +5335,36 @@
       <c r="H28" s="57">
         <v>7</v>
       </c>
-      <c r="I28" s="53">
+      <c r="I28" s="75">
         <v>5.5</v>
       </c>
-      <c r="J28" s="53">
+      <c r="J28" s="80">
+        <v>5.5</v>
+      </c>
+      <c r="K28" s="53">
         <f t="shared" si="0"/>
         <v>6.5</v>
       </c>
-      <c r="K28" s="6">
-        <f>0.25*L28+0.75*M28</f>
+      <c r="L28" s="6">
+        <f>0.25*M28+0.75*N28</f>
         <v>6.5</v>
       </c>
-      <c r="L28" s="69">
-        <f>(T28+V28)/2</f>
-        <v>5</v>
-      </c>
       <c r="M28" s="69">
+        <f>(U28+W28)/2</f>
+        <v>5</v>
+      </c>
+      <c r="N28" s="69">
         <v>7</v>
       </c>
-      <c r="N28" s="69">
-        <f>N27</f>
+      <c r="O28" s="69">
+        <f>O27</f>
         <v>0</v>
       </c>
-      <c r="T28" s="5">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="U28" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="str">
         <f>_xlfn.CONCAT(B29,"  ",C29)</f>
         <v>JULIA  SANTOS OLIVEIRA</v>
@@ -5237,35 +5389,38 @@
         <v>3</v>
       </c>
       <c r="I29" s="53">
+        <v>6.5</v>
+      </c>
+      <c r="J29" s="80">
         <v>5.5</v>
       </c>
-      <c r="J29" s="53">
+      <c r="K29" s="53">
         <f t="shared" si="0"/>
         <v>9.5</v>
       </c>
-      <c r="K29" s="6">
-        <f>0.25*L29+0.75*M29</f>
+      <c r="L29" s="6">
+        <f>0.25*M29+0.75*N29</f>
         <v>9.25</v>
       </c>
-      <c r="L29" s="69">
-        <f>(T29+V29)/2</f>
-        <v>10</v>
-      </c>
       <c r="M29" s="69">
+        <f>(U29+W29)/2</f>
+        <v>10</v>
+      </c>
+      <c r="N29" s="69">
         <v>9</v>
       </c>
-      <c r="N29" s="69">
-        <f>N28</f>
+      <c r="O29" s="69">
+        <f>O28</f>
         <v>0</v>
       </c>
-      <c r="T29" s="5">
-        <v>10</v>
-      </c>
-      <c r="V29" s="5">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="U29" s="5">
+        <v>10</v>
+      </c>
+      <c r="W29" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A30" s="18" t="str">
         <f>_xlfn.CONCAT(B30,"  ",C30)</f>
         <v>LARISSA  YURI SATO</v>
@@ -5290,42 +5445,45 @@
         <v>3</v>
       </c>
       <c r="I30" s="54">
+        <v>7</v>
+      </c>
+      <c r="J30" s="79">
         <v>6</v>
       </c>
-      <c r="J30" s="54">
+      <c r="K30" s="54">
         <f t="shared" si="0"/>
         <v>9.5</v>
       </c>
-      <c r="K30" s="55">
-        <f>0.25*L30+0.75*M30</f>
+      <c r="L30" s="55">
+        <f>0.25*M30+0.75*N30</f>
         <v>9.25</v>
       </c>
-      <c r="L30" s="72">
-        <f>(T30+V30)/2</f>
-        <v>10</v>
-      </c>
       <c r="M30" s="72">
+        <f>(U30+W30)/2</f>
+        <v>10</v>
+      </c>
+      <c r="N30" s="72">
         <v>9</v>
       </c>
-      <c r="N30" s="72">
-        <f>N29</f>
+      <c r="O30" s="72">
+        <f>O29</f>
         <v>0</v>
       </c>
-      <c r="O30" s="73"/>
-      <c r="P30" s="59"/>
+      <c r="P30" s="73"/>
       <c r="Q30" s="59"/>
       <c r="R30" s="59"/>
-      <c r="S30" s="62"/>
-      <c r="T30" s="22">
-        <v>10</v>
-      </c>
-      <c r="U30" s="22"/>
-      <c r="V30" s="22">
-        <v>10</v>
-      </c>
-      <c r="W30" s="33"/>
-    </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="S30" s="59"/>
+      <c r="T30" s="62"/>
+      <c r="U30" s="22">
+        <v>10</v>
+      </c>
+      <c r="V30" s="22"/>
+      <c r="W30" s="22">
+        <v>10</v>
+      </c>
+      <c r="X30" s="33"/>
+    </row>
+    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="str">
         <f>_xlfn.CONCAT(B31,"  ",C31)</f>
         <v>LEONARDO  PATRIANI CARDOSO</v>
@@ -5346,32 +5504,35 @@
         <v>7</v>
       </c>
       <c r="I31" s="53">
+        <v>7.5</v>
+      </c>
+      <c r="J31" s="80">
         <v>6.5</v>
       </c>
-      <c r="J31" s="53">
+      <c r="K31" s="53">
         <f t="shared" si="0"/>
         <v>5.5</v>
       </c>
-      <c r="K31" s="6">
-        <f>0.25*L31+0.75*M31</f>
+      <c r="L31" s="6">
+        <f>0.25*M31+0.75*N31</f>
         <v>5.25</v>
       </c>
-      <c r="L31" s="69">
-        <f>(T31+V31)/2</f>
+      <c r="M31" s="69">
+        <f>(U31+W31)/2</f>
         <v>0</v>
       </c>
-      <c r="M31" s="69">
+      <c r="N31" s="69">
         <v>7</v>
       </c>
-      <c r="N31" s="69">
-        <f>N30</f>
+      <c r="O31" s="69">
+        <f>O30</f>
         <v>0</v>
       </c>
-      <c r="T31" s="11"/>
       <c r="U31" s="11"/>
       <c r="V31" s="11"/>
-    </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W31" s="11"/>
+    </row>
+    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A32" s="41" t="str">
         <f>_xlfn.CONCAT(B32,"  ",C32)</f>
         <v>LIVIA  CANTOWITZ</v>
@@ -5390,27 +5551,30 @@
       <c r="G32" s="14"/>
       <c r="H32" s="58"/>
       <c r="I32" s="65">
+        <v>5</v>
+      </c>
+      <c r="J32" s="81">
         <v>4</v>
       </c>
-      <c r="J32" s="53">
+      <c r="K32" s="53">
         <f t="shared" si="0"/>
         <v>1.5</v>
       </c>
-      <c r="K32" s="6">
-        <f>0.25*L32+0.75*M32</f>
+      <c r="L32" s="6">
+        <f>0.25*M32+0.75*N32</f>
         <v>1.25</v>
       </c>
-      <c r="L32" s="69">
-        <f>(T32+V32)/2</f>
-        <v>5</v>
-      </c>
-      <c r="T32" s="44">
-        <v>10</v>
-      </c>
-      <c r="U32" s="44"/>
+      <c r="M32" s="69">
+        <f>(U32+W32)/2</f>
+        <v>5</v>
+      </c>
+      <c r="U32" s="44">
+        <v>10</v>
+      </c>
       <c r="V32" s="44"/>
-    </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W32" s="44"/>
+    </row>
+    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A33" s="41" t="str">
         <f>_xlfn.CONCAT(B33,"  ",C33)</f>
         <v>LUCAS  PIRES DE CAMARGO SARAI</v>
@@ -5435,36 +5599,39 @@
         <v>9</v>
       </c>
       <c r="I33" s="65">
-        <v>10</v>
-      </c>
-      <c r="J33" s="53">
+        <v>11</v>
+      </c>
+      <c r="J33" s="81">
+        <v>10</v>
+      </c>
+      <c r="K33" s="53">
         <f t="shared" si="0"/>
         <v>7.5</v>
       </c>
-      <c r="K33" s="6">
-        <f>0.25*L33+0.75*M33</f>
+      <c r="L33" s="6">
+        <f>0.25*M33+0.75*N33</f>
         <v>7.375</v>
       </c>
-      <c r="L33" s="69">
-        <f>(T33+V33)/2</f>
-        <v>10</v>
-      </c>
       <c r="M33" s="69">
+        <f>(U33+W33)/2</f>
+        <v>10</v>
+      </c>
+      <c r="N33" s="69">
         <v>6.5</v>
       </c>
-      <c r="N33" s="69">
-        <f>N32</f>
+      <c r="O33" s="69">
+        <f>O32</f>
         <v>0</v>
       </c>
-      <c r="T33" s="44">
-        <v>10</v>
-      </c>
-      <c r="U33" s="44"/>
-      <c r="V33" s="44">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="U33" s="44">
+        <v>10</v>
+      </c>
+      <c r="V33" s="44"/>
+      <c r="W33" s="44">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="str">
         <f>_xlfn.CONCAT(B34,"  ",C34)</f>
         <v>MARCO  ANTONIO DE CAMARGO</v>
@@ -5489,35 +5656,38 @@
         <v>1</v>
       </c>
       <c r="I34" s="53">
+        <v>7</v>
+      </c>
+      <c r="J34" s="80">
         <v>6</v>
       </c>
-      <c r="J34" s="53">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="K34" s="6">
-        <f>0.25*L34+0.75*M34</f>
+      <c r="K34" s="53">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="L34" s="6">
+        <f>0.25*M34+0.75*N34</f>
         <v>9.875</v>
       </c>
-      <c r="L34" s="69">
-        <f>(T34+V34)/2</f>
+      <c r="M34" s="69">
+        <f>(U34+W34)/2</f>
         <v>9.5</v>
       </c>
-      <c r="M34" s="69">
-        <v>10</v>
-      </c>
       <c r="N34" s="69">
-        <f>N33</f>
+        <v>10</v>
+      </c>
+      <c r="O34" s="69">
+        <f>O33</f>
         <v>0</v>
       </c>
-      <c r="T34" s="5">
-        <v>10</v>
-      </c>
-      <c r="V34" s="5">
+      <c r="U34" s="5">
+        <v>10</v>
+      </c>
+      <c r="W34" s="5">
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A35" s="18" t="str">
         <f>_xlfn.CONCAT(B35,"  ",C35)</f>
         <v>MARINA  BARROCA</v>
@@ -5541,51 +5711,54 @@
       <c r="H35" s="59">
         <v>10</v>
       </c>
-      <c r="I35" s="54">
+      <c r="I35" s="76">
         <v>4.5</v>
       </c>
-      <c r="J35" s="54">
+      <c r="J35" s="79">
+        <v>4.5</v>
+      </c>
+      <c r="K35" s="54">
         <f t="shared" si="0"/>
         <v>7.5</v>
       </c>
-      <c r="K35" s="55">
-        <f>0.25*L35+0.75*M35</f>
+      <c r="L35" s="55">
+        <f>0.25*M35+0.75*N35</f>
         <v>7.375</v>
       </c>
-      <c r="L35" s="72">
-        <f>(T35+V35)/2</f>
-        <v>10</v>
-      </c>
       <c r="M35" s="72">
+        <f>(U35+W35)/2</f>
+        <v>10</v>
+      </c>
+      <c r="N35" s="72">
         <v>6.5</v>
       </c>
-      <c r="N35" s="72">
-        <f>SUM(P35,Q35,R35)</f>
+      <c r="O35" s="72">
+        <f>SUM(Q35,R35,S35)</f>
         <v>6.5</v>
       </c>
-      <c r="O35" s="73" t="s">
+      <c r="P35" s="73" t="s">
         <v>190</v>
       </c>
-      <c r="P35" s="59">
+      <c r="Q35" s="59">
         <v>1.5</v>
-      </c>
-      <c r="Q35" s="59">
-        <v>2.5</v>
       </c>
       <c r="R35" s="59">
         <v>2.5</v>
       </c>
-      <c r="S35" s="62"/>
-      <c r="T35" s="22">
-        <v>10</v>
-      </c>
-      <c r="U35" s="22"/>
-      <c r="V35" s="22">
-        <v>10</v>
-      </c>
-      <c r="W35" s="33"/>
-    </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="S35" s="59">
+        <v>2.5</v>
+      </c>
+      <c r="T35" s="62"/>
+      <c r="U35" s="22">
+        <v>10</v>
+      </c>
+      <c r="V35" s="22"/>
+      <c r="W35" s="22">
+        <v>10</v>
+      </c>
+      <c r="X35" s="33"/>
+    </row>
+    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="str">
         <f>_xlfn.CONCAT(B36,"  ",C36)</f>
         <v>MATHEUS  HENRIQUE DE OLIVEIRA SANTOS</v>
@@ -5606,34 +5779,37 @@
         <v>10</v>
       </c>
       <c r="I36" s="53">
+        <v>4</v>
+      </c>
+      <c r="J36" s="80">
         <v>3</v>
       </c>
-      <c r="J36" s="53">
+      <c r="K36" s="53">
         <f t="shared" si="0"/>
         <v>6.5</v>
       </c>
-      <c r="K36" s="6">
-        <f>0.25*L36+0.75*M36</f>
+      <c r="L36" s="6">
+        <f>0.25*M36+0.75*N36</f>
         <v>6.125</v>
       </c>
-      <c r="L36" s="69">
-        <f>(T36+V36)/2</f>
-        <v>5</v>
-      </c>
       <c r="M36" s="69">
+        <f>(U36+W36)/2</f>
+        <v>5</v>
+      </c>
+      <c r="N36" s="69">
         <v>6.5</v>
       </c>
-      <c r="N36" s="69">
-        <f>N35</f>
+      <c r="O36" s="69">
+        <f>O35</f>
         <v>6.5</v>
       </c>
-      <c r="T36" s="11" t="s">
+      <c r="U36" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="U36" s="11"/>
       <c r="V36" s="11"/>
-    </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W36" s="11"/>
+    </row>
+    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A37" s="41" t="str">
         <f>_xlfn.CONCAT(B37,"  ",C37)</f>
         <v>NATAN  MOREIRA PASSOS</v>
@@ -5654,34 +5830,35 @@
         <v>1</v>
       </c>
       <c r="I37" s="65"/>
-      <c r="J37" s="53">
+      <c r="J37" s="81"/>
+      <c r="K37" s="53">
         <f t="shared" si="0"/>
         <v>8.5</v>
       </c>
-      <c r="K37" s="6">
-        <f>0.25*L37+0.75*M37</f>
+      <c r="L37" s="6">
+        <f>0.25*M37+0.75*N37</f>
         <v>8.375</v>
       </c>
-      <c r="L37" s="69">
-        <f>(T37+V37)/2</f>
+      <c r="M37" s="69">
+        <f>(U37+W37)/2</f>
         <v>3.5</v>
       </c>
-      <c r="M37" s="69">
-        <v>10</v>
-      </c>
       <c r="N37" s="69">
-        <f>N36</f>
+        <v>10</v>
+      </c>
+      <c r="O37" s="69">
+        <f>O36</f>
         <v>6.5</v>
       </c>
-      <c r="T37" s="44">
+      <c r="U37" s="44">
         <v>7</v>
       </c>
-      <c r="U37" s="49" t="s">
+      <c r="V37" s="49" t="s">
         <v>203</v>
       </c>
-      <c r="V37" s="49"/>
-    </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W37" s="49"/>
+    </row>
+    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="str">
         <f>_xlfn.CONCAT(B38,"  ",C38)</f>
         <v>NICOLAS  HENRIQUES DE ALMEIDA</v>
@@ -5706,35 +5883,38 @@
         <v>1</v>
       </c>
       <c r="I38" s="53">
+        <v>7.5</v>
+      </c>
+      <c r="J38" s="80">
         <v>6.5</v>
       </c>
-      <c r="J38" s="53">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="K38" s="6">
-        <f>0.25*L38+0.75*M38</f>
-        <v>10</v>
-      </c>
-      <c r="L38" s="69">
-        <f>(T38+V38)/2</f>
+      <c r="K38" s="53">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="L38" s="6">
+        <f>0.25*M38+0.75*N38</f>
         <v>10</v>
       </c>
       <c r="M38" s="69">
+        <f>(U38+W38)/2</f>
         <v>10</v>
       </c>
       <c r="N38" s="69">
-        <f>N37</f>
+        <v>10</v>
+      </c>
+      <c r="O38" s="69">
+        <f>O37</f>
         <v>6.5</v>
       </c>
-      <c r="T38" s="5">
-        <v>10</v>
-      </c>
-      <c r="V38" s="5">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="U38" s="5">
+        <v>10</v>
+      </c>
+      <c r="W38" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="str">
         <f>_xlfn.CONCAT(B39,"  ",C39)</f>
         <v>OTAVIO  AUGUSTO FREIRE DE ANDRADE BRUZADI</v>
@@ -5759,35 +5939,38 @@
         <v>9</v>
       </c>
       <c r="I39" s="53">
+        <v>7.5</v>
+      </c>
+      <c r="J39" s="80">
         <v>6.5</v>
       </c>
-      <c r="J39" s="53">
+      <c r="K39" s="53">
         <f t="shared" si="0"/>
         <v>7.5</v>
       </c>
-      <c r="K39" s="6">
-        <f>0.25*L39+0.75*M39</f>
+      <c r="L39" s="6">
+        <f>0.25*M39+0.75*N39</f>
         <v>7.375</v>
       </c>
-      <c r="L39" s="69">
-        <f>(T39+V39)/2</f>
-        <v>10</v>
-      </c>
       <c r="M39" s="69">
+        <f>(U39+W39)/2</f>
+        <v>10</v>
+      </c>
+      <c r="N39" s="69">
         <v>6.5</v>
       </c>
-      <c r="N39" s="69">
-        <f>N38</f>
+      <c r="O39" s="69">
+        <f>O38</f>
         <v>6.5</v>
       </c>
-      <c r="T39" s="5">
-        <v>10</v>
-      </c>
-      <c r="V39" s="5">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="U39" s="5">
+        <v>10</v>
+      </c>
+      <c r="W39" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A40" s="18" t="str">
         <f>_xlfn.CONCAT(B40,"  ",C40)</f>
         <v>THOMAS  PINHEIRO GRANDIN</v>
@@ -5808,38 +5991,41 @@
         <v>1</v>
       </c>
       <c r="I40" s="54">
+        <v>5.5</v>
+      </c>
+      <c r="J40" s="79">
         <v>4.5</v>
       </c>
-      <c r="J40" s="54">
+      <c r="K40" s="54">
         <f t="shared" si="0"/>
         <v>7.5</v>
       </c>
-      <c r="K40" s="55">
-        <f>0.25*L40+0.75*M40</f>
+      <c r="L40" s="55">
+        <f>0.25*M40+0.75*N40</f>
         <v>7.5</v>
       </c>
-      <c r="L40" s="72">
-        <f>(T40+V40)/2</f>
+      <c r="M40" s="72">
+        <f>(U40+W40)/2</f>
         <v>0</v>
       </c>
-      <c r="M40" s="72">
-        <v>10</v>
-      </c>
       <c r="N40" s="72">
-        <f>N39</f>
+        <v>10</v>
+      </c>
+      <c r="O40" s="72">
+        <f>O39</f>
         <v>6.5</v>
       </c>
-      <c r="O40" s="73"/>
-      <c r="P40" s="59"/>
+      <c r="P40" s="73"/>
       <c r="Q40" s="59"/>
       <c r="R40" s="59"/>
-      <c r="S40" s="62"/>
-      <c r="T40" s="22"/>
+      <c r="S40" s="59"/>
+      <c r="T40" s="62"/>
       <c r="U40" s="22"/>
       <c r="V40" s="22"/>
-      <c r="W40" s="33"/>
-    </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W40" s="22"/>
+      <c r="X40" s="33"/>
+    </row>
+    <row r="41" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="str">
         <f>_xlfn.CONCAT(B41,"  ",C41)</f>
         <v>TIAGO  SILVEIRA LOPES</v>
@@ -5863,33 +6049,36 @@
       <c r="H41" s="57">
         <v>6</v>
       </c>
-      <c r="I41" s="53">
+      <c r="I41" s="75">
         <v>4</v>
       </c>
-      <c r="J41" s="53">
+      <c r="J41" s="80">
+        <v>4</v>
+      </c>
+      <c r="K41" s="53">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="K41" s="6">
-        <f>0.25*L41+0.75*M41</f>
+      <c r="L41" s="6">
+        <f>0.25*M41+0.75*N41</f>
         <v>5.75</v>
       </c>
-      <c r="L41" s="69">
-        <f>(T41+V41)/2</f>
-        <v>5</v>
-      </c>
       <c r="M41" s="69">
+        <f>(U41+W41)/2</f>
+        <v>5</v>
+      </c>
+      <c r="N41" s="69">
         <v>6</v>
       </c>
-      <c r="N41" s="69">
-        <f>N40</f>
+      <c r="O41" s="69">
+        <f>O40</f>
         <v>6.5</v>
       </c>
-      <c r="T41" s="5">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="U41" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A42" s="18" t="str">
         <f>_xlfn.CONCAT(B42,"  ",C42)</f>
         <v>VITOR  ALVES PEREIRA</v>
@@ -5914,52 +6103,61 @@
         <v>4</v>
       </c>
       <c r="I42" s="54">
+        <v>4</v>
+      </c>
+      <c r="J42" s="79">
         <v>3</v>
       </c>
-      <c r="J42" s="54">
+      <c r="K42" s="54">
         <f t="shared" si="0"/>
         <v>8.5</v>
       </c>
-      <c r="K42" s="55">
-        <f>0.25*L42+0.75*M42</f>
+      <c r="L42" s="55">
+        <f>0.25*M42+0.75*N42</f>
         <v>8.125</v>
       </c>
-      <c r="L42" s="72">
-        <f>(T42+V42)/2</f>
-        <v>10</v>
-      </c>
       <c r="M42" s="72">
+        <f>(U42+W42)/2</f>
+        <v>10</v>
+      </c>
+      <c r="N42" s="72">
         <v>7.5</v>
       </c>
-      <c r="N42" s="72">
-        <f>N41</f>
+      <c r="O42" s="72">
+        <f>O41</f>
         <v>6.5</v>
       </c>
-      <c r="O42" s="73"/>
-      <c r="P42" s="59"/>
+      <c r="P42" s="73"/>
       <c r="Q42" s="59"/>
       <c r="R42" s="59"/>
-      <c r="S42" s="62"/>
-      <c r="T42" s="22">
-        <v>10</v>
-      </c>
-      <c r="U42" s="22"/>
-      <c r="V42" s="22">
-        <v>10</v>
-      </c>
-      <c r="W42" s="33"/>
-    </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="J43" s="53"/>
-      <c r="K43" s="6"/>
-    </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="J44" s="53"/>
-      <c r="K44" s="6"/>
+      <c r="S42" s="59"/>
+      <c r="T42" s="62"/>
+      <c r="U42" s="22">
+        <v>10</v>
+      </c>
+      <c r="V42" s="22"/>
+      <c r="W42" s="22">
+        <v>10</v>
+      </c>
+      <c r="X42" s="33"/>
+    </row>
+    <row r="43" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="I43" s="53" t="s">
+        <v>8</v>
+      </c>
+      <c r="K43" s="53"/>
+      <c r="L43" s="6"/>
+    </row>
+    <row r="44" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="I44" s="53" t="s">
+        <v>8</v>
+      </c>
+      <c r="K44" s="53"/>
+      <c r="L44" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S44" xr:uid="{976B32EA-1F52-46D5-9E73-D7BC92A42345}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S44">
+  <autoFilter ref="A1:T44" xr:uid="{976B32EA-1F52-46D5-9E73-D7BC92A42345}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:T44">
       <sortCondition ref="A1:A44"/>
     </sortState>
   </autoFilter>
@@ -6000,163 +6198,222 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A98778EE-FBFC-4E47-98AB-2B66B2949A66}">
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="50.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="47.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="50.85546875" style="78" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="47.7109375" style="78" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="50.85546875" style="78" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="78"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="75" t="s">
+    <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="77" t="s">
         <v>214</v>
       </c>
-      <c r="B1" s="75" t="s">
+      <c r="B1" s="77" t="s">
         <v>249</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="C1" s="77" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="78" t="s">
         <v>215</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="78" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="C2" s="78" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="78" t="s">
         <v>216</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="78" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="C3" s="78" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="78" t="s">
         <v>217</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="78" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="78" t="s">
         <v>218</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="78" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="C5" s="78" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="78" t="s">
         <v>219</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="78" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="C6" s="78" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="78" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" s="74" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C7" s="78" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="74" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="C8" s="74"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="78" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="C9" s="78" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="78" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="C10" s="78" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="78" t="s">
         <v>224</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="78" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="C11" s="78" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="78" t="s">
         <v>225</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="78" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" s="74" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C12" s="78" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="74" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="C13" s="74"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="78" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="C14" s="78" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="78" t="s">
         <v>228</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="78" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C15" s="78" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="74" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="C16" s="74"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="78" t="s">
         <v>230</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="78" t="s">
         <v>244</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="C17" s="78" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="78" t="s">
         <v>231</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="78" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="C18" s="78" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="78" t="s">
         <v>232</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="78" t="s">
         <v>246</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="C19" s="78" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="78" t="s">
         <v>233</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="78" t="s">
         <v>247</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="C20" s="78" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="78" t="s">
         <v>234</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="78" t="s">
         <v>248</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="C21" s="78" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="78" t="s">
         <v>235</v>
+      </c>
+      <c r="C22" s="78" t="s">
+        <v>261</v>
       </c>
     </row>
   </sheetData>

--- a/Notas_N1_e_N2.xlsx
+++ b/Notas_N1_e_N2.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\ano_2026S1\IA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{300171CD-AF18-4244-8D6B-3647E69F786D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20AE5444-A64F-4B10-817F-86F1FDDF71D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Notas B1" sheetId="1" r:id="rId1"/>
     <sheet name="Notas B2" sheetId="2" r:id="rId2"/>
-    <sheet name="SUB e PF" sheetId="3" r:id="rId3"/>
+    <sheet name="Notas SUB" sheetId="4" r:id="rId3"/>
+    <sheet name=" " sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Notas B1'!$A$1:$N$42</definedName>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="264">
   <si>
     <t>Nome</t>
   </si>
@@ -828,6 +829,12 @@
   </si>
   <si>
     <t>10410862 VITOR ALVES PEREIRA 4,8</t>
+  </si>
+  <si>
+    <t>Nota</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
 </sst>
 </file>
@@ -837,7 +844,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -946,6 +953,32 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF0070C0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0070C0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -977,7 +1010,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
@@ -1069,32 +1102,10 @@
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1112,24 +1123,15 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1138,7 +1140,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1167,7 +1169,12 @@
     <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -3718,16 +3725,16 @@
     <col min="3" max="5" width="9.140625" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="5.5703125" style="4" hidden="1" customWidth="1"/>
     <col min="7" max="7" width="9.140625" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="4.85546875" style="57" customWidth="1"/>
-    <col min="9" max="9" width="10.28515625" style="53" customWidth="1"/>
-    <col min="10" max="10" width="10.28515625" style="80" customWidth="1"/>
-    <col min="11" max="11" width="10.140625" style="66" customWidth="1"/>
+    <col min="8" max="8" width="4.85546875" style="47" customWidth="1"/>
+    <col min="9" max="9" width="10.28515625" style="43" customWidth="1"/>
+    <col min="10" max="10" width="10.28515625" style="67" customWidth="1"/>
+    <col min="11" max="11" width="10.140625" style="53" customWidth="1"/>
     <col min="12" max="12" width="10.140625" style="5" hidden="1" customWidth="1"/>
-    <col min="13" max="14" width="10.140625" style="69" customWidth="1"/>
-    <col min="15" max="15" width="1.42578125" style="71" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="31.7109375" style="70" bestFit="1" customWidth="1"/>
-    <col min="17" max="19" width="8" style="57" customWidth="1"/>
-    <col min="20" max="20" width="9.140625" style="63"/>
+    <col min="13" max="14" width="10.140625" style="56" customWidth="1"/>
+    <col min="15" max="15" width="1.42578125" style="58" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="31.7109375" style="57" bestFit="1" customWidth="1"/>
+    <col min="17" max="19" width="8" style="47" customWidth="1"/>
+    <col min="20" max="20" width="9.140625" style="51"/>
     <col min="21" max="21" width="7.85546875" style="5" customWidth="1"/>
     <col min="22" max="22" width="13.42578125" style="5" customWidth="1"/>
     <col min="23" max="23" width="5.85546875" style="5" customWidth="1"/>
@@ -3755,16 +3762,16 @@
       <c r="G1" s="27" t="s">
         <v>154</v>
       </c>
-      <c r="H1" s="56" t="s">
+      <c r="H1" s="46" t="s">
         <v>155</v>
       </c>
-      <c r="I1" s="54" t="s">
+      <c r="I1" s="44" t="s">
         <v>213</v>
       </c>
-      <c r="J1" s="79" t="s">
+      <c r="J1" s="66" t="s">
         <v>213</v>
       </c>
-      <c r="K1" s="64" t="s">
+      <c r="K1" s="52" t="s">
         <v>211</v>
       </c>
       <c r="L1" s="29" t="s">
@@ -3776,22 +3783,22 @@
       <c r="N1" s="34" t="s">
         <v>200</v>
       </c>
-      <c r="O1" s="67" t="s">
+      <c r="O1" s="54" t="s">
         <v>201</v>
       </c>
-      <c r="P1" s="68" t="s">
+      <c r="P1" s="55" t="s">
         <v>207</v>
       </c>
-      <c r="Q1" s="59" t="s">
+      <c r="Q1" s="48" t="s">
         <v>185</v>
       </c>
-      <c r="R1" s="59" t="s">
+      <c r="R1" s="48" t="s">
         <v>184</v>
       </c>
-      <c r="S1" s="59" t="s">
+      <c r="S1" s="48" t="s">
         <v>186</v>
       </c>
-      <c r="T1" s="62"/>
+      <c r="T1" s="50"/>
       <c r="U1" s="29" t="s">
         <v>206</v>
       </c>
@@ -3805,7 +3812,7 @@
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="str">
-        <f>_xlfn.CONCAT(B2,"  ",C2)</f>
+        <f t="shared" ref="A2:A42" si="0">_xlfn.CONCAT(B2,"  ",C2)</f>
         <v>ALEX  KAZUO KODAMA</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -3826,47 +3833,47 @@
       <c r="G2" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="H2" s="57">
+      <c r="H2" s="47">
         <v>1</v>
       </c>
-      <c r="I2" s="75">
+      <c r="I2" s="62">
         <v>6</v>
       </c>
-      <c r="J2" s="80">
+      <c r="J2" s="67">
         <v>6</v>
       </c>
-      <c r="K2" s="53">
+      <c r="K2" s="43">
         <f>_xlfn.CEILING.MATH(L2,0.5)</f>
         <v>10</v>
       </c>
       <c r="L2" s="6">
-        <f>0.25*M2+0.75*N2</f>
-        <v>10</v>
-      </c>
-      <c r="M2" s="69">
-        <f>(U2+W2)/2</f>
-        <v>10</v>
-      </c>
-      <c r="N2" s="69">
-        <v>10</v>
-      </c>
-      <c r="O2" s="69">
+        <f t="shared" ref="L2:L42" si="1">0.25*M2+0.75*N2</f>
+        <v>10</v>
+      </c>
+      <c r="M2" s="56">
+        <f t="shared" ref="M2:M10" si="2">(U2+W2)/2</f>
+        <v>10</v>
+      </c>
+      <c r="N2" s="56">
+        <v>10</v>
+      </c>
+      <c r="O2" s="56">
         <f>SUM(Q2,R2,S2)</f>
         <v>10</v>
       </c>
-      <c r="P2" s="70" t="s">
+      <c r="P2" s="57" t="s">
         <v>188</v>
       </c>
-      <c r="Q2" s="57">
+      <c r="Q2" s="47">
         <v>3</v>
       </c>
-      <c r="R2" s="57">
+      <c r="R2" s="47">
         <v>3.5</v>
       </c>
-      <c r="S2" s="57">
+      <c r="S2" s="47">
         <v>3.5</v>
       </c>
-      <c r="T2" s="63" t="s">
+      <c r="T2" s="51" t="s">
         <v>187</v>
       </c>
       <c r="U2" s="5">
@@ -3877,71 +3884,67 @@
       </c>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A3" s="41" t="str">
-        <f>_xlfn.CONCAT(B3,"  ",C3)</f>
+      <c r="A3" s="7" t="str">
+        <f t="shared" si="0"/>
         <v>ANDRE  MOREIRA GUIMARAES</v>
       </c>
-      <c r="B3" s="42" t="s">
+      <c r="B3" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C3" s="42" t="s">
+      <c r="C3" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42" t="s">
+      <c r="D3" s="1"/>
+      <c r="E3" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="F3" s="43"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="58">
+      <c r="H3" s="47">
         <v>7</v>
       </c>
-      <c r="I3" s="65">
-        <v>10</v>
-      </c>
-      <c r="J3" s="81">
+      <c r="I3" s="43">
+        <v>10</v>
+      </c>
+      <c r="J3" s="67">
         <v>9</v>
       </c>
-      <c r="K3" s="53">
-        <f t="shared" ref="K3:K42" si="0">_xlfn.CEILING.MATH(L3,0.5)</f>
+      <c r="K3" s="43">
+        <f t="shared" ref="K3:K42" si="3">_xlfn.CEILING.MATH(L3,0.5)</f>
         <v>6.5</v>
       </c>
       <c r="L3" s="6">
-        <f>0.25*M3+0.75*N3</f>
+        <f t="shared" si="1"/>
         <v>6.5</v>
       </c>
-      <c r="M3" s="69">
-        <f>(U3+W3)/2</f>
-        <v>5</v>
-      </c>
-      <c r="N3" s="69">
+      <c r="M3" s="56">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="N3" s="56">
         <v>7</v>
       </c>
-      <c r="O3" s="69">
+      <c r="O3" s="56">
         <f>SUM(Q3,R3,S3)</f>
         <v>7</v>
       </c>
-      <c r="P3" s="70" t="s">
+      <c r="P3" s="57" t="s">
         <v>191</v>
       </c>
-      <c r="Q3" s="57">
+      <c r="Q3" s="47">
         <v>2</v>
       </c>
-      <c r="R3" s="57">
+      <c r="R3" s="47">
         <v>2.5</v>
       </c>
-      <c r="S3" s="57">
+      <c r="S3" s="47">
         <v>2.5</v>
       </c>
-      <c r="U3" s="44">
-        <v>10</v>
-      </c>
-      <c r="V3" s="44"/>
-      <c r="W3" s="44"/>
+      <c r="U3" s="5">
+        <v>10</v>
+      </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="str">
-        <f>_xlfn.CONCAT(B4,"  ",C4)</f>
+        <f t="shared" si="0"/>
         <v>ANNA  LUIZA STELLA SANTOS</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -3960,25 +3963,25 @@
       <c r="G4" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="H4" s="57">
+      <c r="H4" s="47">
         <v>2</v>
       </c>
-      <c r="I4" s="53">
-        <v>5</v>
-      </c>
-      <c r="J4" s="80">
+      <c r="I4" s="43">
+        <v>5</v>
+      </c>
+      <c r="J4" s="67">
         <v>4</v>
       </c>
-      <c r="K4" s="53">
-        <f t="shared" si="0"/>
+      <c r="K4" s="43">
+        <f t="shared" si="3"/>
         <v>1.5</v>
       </c>
       <c r="L4" s="6">
-        <f>0.25*M4+0.75*N4</f>
+        <f t="shared" si="1"/>
         <v>1.25</v>
       </c>
-      <c r="M4" s="69">
-        <f>(U4+W4)/2</f>
+      <c r="M4" s="56">
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="U4" s="5">
@@ -3987,7 +3990,7 @@
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" s="18" t="str">
-        <f>_xlfn.CONCAT(B5,"  ",C5)</f>
+        <f t="shared" si="0"/>
         <v>BEATRIZ  LIMA DE MOURA</v>
       </c>
       <c r="B5" s="19" t="s">
@@ -4006,47 +4009,47 @@
       <c r="G5" s="21" t="s">
         <v>124</v>
       </c>
-      <c r="H5" s="59">
+      <c r="H5" s="48">
         <v>3</v>
       </c>
-      <c r="I5" s="54">
+      <c r="I5" s="44">
         <v>5.5</v>
       </c>
-      <c r="J5" s="79">
+      <c r="J5" s="66">
         <v>4.5</v>
       </c>
-      <c r="K5" s="54">
-        <f t="shared" si="0"/>
+      <c r="K5" s="44">
+        <f t="shared" si="3"/>
         <v>9.5</v>
       </c>
-      <c r="L5" s="55">
-        <f>0.25*M5+0.75*N5</f>
+      <c r="L5" s="45">
+        <f t="shared" si="1"/>
         <v>9.125</v>
       </c>
-      <c r="M5" s="72">
-        <f>(U5+W5)/2</f>
+      <c r="M5" s="59">
+        <f t="shared" si="2"/>
         <v>9.5</v>
       </c>
-      <c r="N5" s="72">
+      <c r="N5" s="59">
         <v>9</v>
       </c>
-      <c r="O5" s="72">
+      <c r="O5" s="59">
         <f>SUM(Q5,R5,S5)</f>
         <v>9</v>
       </c>
-      <c r="P5" s="73" t="s">
+      <c r="P5" s="60" t="s">
         <v>189</v>
       </c>
-      <c r="Q5" s="59">
+      <c r="Q5" s="48">
         <v>3</v>
       </c>
-      <c r="R5" s="59">
+      <c r="R5" s="48">
         <v>3.5</v>
       </c>
-      <c r="S5" s="59">
+      <c r="S5" s="48">
         <v>2.5</v>
       </c>
-      <c r="T5" s="62" t="s">
+      <c r="T5" s="50" t="s">
         <v>197</v>
       </c>
       <c r="U5" s="22">
@@ -4060,7 +4063,7 @@
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="str">
-        <f>_xlfn.CONCAT(B6,"  ",C6)</f>
+        <f t="shared" si="0"/>
         <v>BERNARDO  SOUZA OLIVEIRA</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -4079,31 +4082,31 @@
       <c r="G6" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="H6" s="60">
+      <c r="H6" s="49">
         <v>7</v>
       </c>
-      <c r="I6" s="53">
+      <c r="I6" s="43">
         <v>9.5</v>
       </c>
-      <c r="J6" s="80">
+      <c r="J6" s="67">
         <v>8.5</v>
       </c>
-      <c r="K6" s="53">
-        <f t="shared" si="0"/>
+      <c r="K6" s="43">
+        <f t="shared" si="3"/>
         <v>7.5</v>
       </c>
       <c r="L6" s="6">
-        <f>0.25*M6+0.75*N6</f>
+        <f t="shared" si="1"/>
         <v>7.25</v>
       </c>
-      <c r="M6" s="69">
-        <f>(U6+W6)/2</f>
+      <c r="M6" s="56">
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="N6" s="69">
+      <c r="N6" s="56">
         <v>7</v>
       </c>
-      <c r="O6" s="69">
+      <c r="O6" s="56">
         <f>O5</f>
         <v>9</v>
       </c>
@@ -4111,13 +4114,13 @@
         <v>202</v>
       </c>
       <c r="V6" s="11"/>
-      <c r="W6" s="51" t="s">
+      <c r="W6" s="42" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="str">
-        <f>_xlfn.CONCAT(B7,"  ",C7)</f>
+        <f t="shared" si="0"/>
         <v>BRUNA  AGUIAR MUCHIUTI</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -4136,44 +4139,44 @@
       <c r="G7" s="14" t="s">
         <v>150</v>
       </c>
-      <c r="H7" s="57">
+      <c r="H7" s="47">
         <v>9</v>
       </c>
-      <c r="I7" s="53">
-        <v>5</v>
-      </c>
-      <c r="J7" s="80">
+      <c r="I7" s="43">
+        <v>5</v>
+      </c>
+      <c r="J7" s="67">
         <v>4</v>
       </c>
-      <c r="K7" s="53">
-        <f t="shared" si="0"/>
+      <c r="K7" s="43">
+        <f t="shared" si="3"/>
         <v>7.5</v>
       </c>
       <c r="L7" s="6">
-        <f>0.25*M7+0.75*N7</f>
+        <f t="shared" si="1"/>
         <v>7.375</v>
       </c>
-      <c r="M7" s="69">
-        <f>(U7+W7)/2</f>
-        <v>10</v>
-      </c>
-      <c r="N7" s="69">
+      <c r="M7" s="56">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="N7" s="56">
         <v>6.5</v>
       </c>
-      <c r="O7" s="69">
+      <c r="O7" s="56">
         <f>SUM(Q7,R7,S7)</f>
         <v>6.5</v>
       </c>
-      <c r="P7" s="70" t="s">
+      <c r="P7" s="57" t="s">
         <v>194</v>
       </c>
-      <c r="Q7" s="57">
+      <c r="Q7" s="47">
         <v>1.5</v>
       </c>
-      <c r="R7" s="57">
+      <c r="R7" s="47">
         <v>2.5</v>
       </c>
-      <c r="S7" s="57">
+      <c r="S7" s="47">
         <v>2.5</v>
       </c>
       <c r="U7" s="5">
@@ -4185,7 +4188,7 @@
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="str">
-        <f>_xlfn.CONCAT(B8,"  ",C8)</f>
+        <f t="shared" si="0"/>
         <v>BRUNO  ANTICO GALIN</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -4204,44 +4207,44 @@
       <c r="G8" t="s">
         <v>126</v>
       </c>
-      <c r="H8" s="57">
+      <c r="H8" s="47">
         <v>4</v>
       </c>
-      <c r="I8" s="53">
+      <c r="I8" s="43">
         <v>6.5</v>
       </c>
-      <c r="J8" s="80">
+      <c r="J8" s="67">
         <v>5.5</v>
       </c>
-      <c r="K8" s="53">
-        <f t="shared" si="0"/>
+      <c r="K8" s="43">
+        <f t="shared" si="3"/>
         <v>8.5</v>
       </c>
       <c r="L8" s="6">
-        <f>0.25*M8+0.75*N8</f>
+        <f t="shared" si="1"/>
         <v>8.125</v>
       </c>
-      <c r="M8" s="69">
-        <f>(U8+W8)/2</f>
-        <v>10</v>
-      </c>
-      <c r="N8" s="69">
+      <c r="M8" s="56">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="N8" s="56">
         <v>7.5</v>
       </c>
-      <c r="O8" s="69">
+      <c r="O8" s="56">
         <f>SUM(Q8,R8,S8)</f>
         <v>7.5</v>
       </c>
-      <c r="P8" s="70" t="s">
+      <c r="P8" s="57" t="s">
         <v>193</v>
       </c>
-      <c r="Q8" s="57">
+      <c r="Q8" s="47">
         <v>2.5</v>
       </c>
-      <c r="R8" s="57">
+      <c r="R8" s="47">
         <v>2.5</v>
       </c>
-      <c r="S8" s="57">
+      <c r="S8" s="47">
         <v>2.5</v>
       </c>
       <c r="U8" s="5">
@@ -4253,7 +4256,7 @@
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="str">
-        <f>_xlfn.CONCAT(B9,"  ",C9)</f>
+        <f t="shared" si="0"/>
         <v>BRUNO  LAUAND FERRAO</v>
       </c>
       <c r="B9" s="1" t="s">
@@ -4272,47 +4275,47 @@
       <c r="G9" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="H9" s="57">
-        <v>5</v>
-      </c>
-      <c r="I9" s="53">
+      <c r="H9" s="47">
+        <v>5</v>
+      </c>
+      <c r="I9" s="43">
         <v>5.5</v>
       </c>
-      <c r="J9" s="80">
+      <c r="J9" s="67">
         <v>4.5</v>
       </c>
-      <c r="K9" s="53">
-        <f t="shared" si="0"/>
+      <c r="K9" s="43">
+        <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="L9" s="6">
-        <f>0.25*M9+0.75*N9</f>
+        <f t="shared" si="1"/>
         <v>9.875</v>
       </c>
-      <c r="M9" s="69">
-        <f>(U9+W9)/2</f>
+      <c r="M9" s="56">
+        <f t="shared" si="2"/>
         <v>9.5</v>
       </c>
-      <c r="N9" s="69">
-        <v>10</v>
-      </c>
-      <c r="O9" s="69">
+      <c r="N9" s="56">
+        <v>10</v>
+      </c>
+      <c r="O9" s="56">
         <f>SUM(Q9,R9,S9)</f>
         <v>10</v>
       </c>
-      <c r="P9" s="70" t="s">
+      <c r="P9" s="57" t="s">
         <v>192</v>
       </c>
-      <c r="Q9" s="57">
+      <c r="Q9" s="47">
         <v>3</v>
       </c>
-      <c r="R9" s="57">
+      <c r="R9" s="47">
         <v>3.5</v>
       </c>
-      <c r="S9" s="57">
+      <c r="S9" s="47">
         <v>3.5</v>
       </c>
-      <c r="T9" s="63" t="s">
+      <c r="T9" s="51" t="s">
         <v>198</v>
       </c>
       <c r="U9" s="5">
@@ -4324,7 +4327,7 @@
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" s="18" t="str">
-        <f>_xlfn.CONCAT(B10,"  ",C10)</f>
+        <f t="shared" si="0"/>
         <v>CAUE  MACEDO DE SOUZA</v>
       </c>
       <c r="B10" s="19" t="s">
@@ -4339,32 +4342,32 @@
       </c>
       <c r="F10" s="20"/>
       <c r="G10" s="21"/>
-      <c r="H10" s="59"/>
-      <c r="I10" s="76">
+      <c r="H10" s="48"/>
+      <c r="I10" s="63">
         <v>3</v>
       </c>
-      <c r="J10" s="79">
+      <c r="J10" s="66">
         <v>3</v>
       </c>
-      <c r="K10" s="54">
-        <f t="shared" si="0"/>
+      <c r="K10" s="44">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L10" s="55">
-        <f>0.25*M10+0.75*N10</f>
+      <c r="L10" s="45">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="M10" s="72">
-        <f>(U10+W10)/2</f>
+      <c r="M10" s="59">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="N10" s="72"/>
-      <c r="O10" s="72"/>
-      <c r="P10" s="73"/>
-      <c r="Q10" s="59"/>
-      <c r="R10" s="59"/>
-      <c r="S10" s="59"/>
-      <c r="T10" s="62"/>
+      <c r="N10" s="59"/>
+      <c r="O10" s="59"/>
+      <c r="P10" s="60"/>
+      <c r="Q10" s="48"/>
+      <c r="R10" s="48"/>
+      <c r="S10" s="48"/>
+      <c r="T10" s="50"/>
       <c r="U10" s="22"/>
       <c r="V10" s="22"/>
       <c r="W10" s="22"/>
@@ -4372,7 +4375,7 @@
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="str">
-        <f>_xlfn.CONCAT(B11,"  ",C11)</f>
+        <f t="shared" si="0"/>
         <v>CLEVERSON  PEREIRA DA SILVA</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -4391,30 +4394,30 @@
       <c r="G11" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="H11" s="60">
+      <c r="H11" s="49">
         <v>4</v>
       </c>
-      <c r="I11" s="53">
+      <c r="I11" s="43">
         <v>4</v>
       </c>
-      <c r="J11" s="80">
+      <c r="J11" s="67">
         <v>3</v>
       </c>
-      <c r="K11" s="53">
-        <f t="shared" si="0"/>
+      <c r="K11" s="43">
+        <f t="shared" si="3"/>
         <v>7.5</v>
       </c>
       <c r="L11" s="6">
-        <f>0.25*M11+0.75*N11</f>
+        <f t="shared" si="1"/>
         <v>7.375</v>
       </c>
-      <c r="M11" s="69">
+      <c r="M11" s="56">
         <v>7</v>
       </c>
-      <c r="N11" s="69">
+      <c r="N11" s="56">
         <v>7.5</v>
       </c>
-      <c r="O11" s="69">
+      <c r="O11" s="56">
         <f>O10</f>
         <v>0</v>
       </c>
@@ -4422,13 +4425,13 @@
         <v>202</v>
       </c>
       <c r="V11" s="11"/>
-      <c r="W11" s="51" t="s">
+      <c r="W11" s="42" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="str">
-        <f>_xlfn.CONCAT(B12,"  ",C12)</f>
+        <f t="shared" si="0"/>
         <v>EDUARDO  OLIVEIRA CARVALHO</v>
       </c>
       <c r="B12" s="1" t="s">
@@ -4447,44 +4450,44 @@
       <c r="G12" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="H12" s="57">
+      <c r="H12" s="47">
         <v>6</v>
       </c>
-      <c r="I12" s="53">
+      <c r="I12" s="43">
         <v>8</v>
       </c>
-      <c r="J12" s="80">
+      <c r="J12" s="67">
         <v>7</v>
       </c>
-      <c r="K12" s="53">
-        <f t="shared" si="0"/>
+      <c r="K12" s="43">
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="L12" s="6">
-        <f>0.25*M12+0.75*N12</f>
+        <f t="shared" si="1"/>
         <v>5.75</v>
       </c>
-      <c r="M12" s="69">
-        <f>(U12+W12)/2</f>
-        <v>5</v>
-      </c>
-      <c r="N12" s="69">
+      <c r="M12" s="56">
+        <f t="shared" ref="M12:M42" si="4">(U12+W12)/2</f>
+        <v>5</v>
+      </c>
+      <c r="N12" s="56">
         <v>6</v>
       </c>
-      <c r="O12" s="69">
+      <c r="O12" s="56">
         <f>SUM(Q12,R12,S12)</f>
         <v>6</v>
       </c>
-      <c r="P12" s="70" t="s">
+      <c r="P12" s="57" t="s">
         <v>196</v>
       </c>
-      <c r="Q12" s="57">
+      <c r="Q12" s="47">
         <v>1.5</v>
       </c>
-      <c r="R12" s="57">
+      <c r="R12" s="47">
         <v>2.5</v>
       </c>
-      <c r="S12" s="57">
+      <c r="S12" s="47">
         <v>2</v>
       </c>
       <c r="W12" s="5">
@@ -4492,65 +4495,64 @@
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A13" s="41" t="str">
-        <f>_xlfn.CONCAT(B13,"  ",C13)</f>
+      <c r="A13" s="7" t="str">
+        <f t="shared" si="0"/>
         <v>EDUARDO  TAKASHI MISSAKA</v>
       </c>
-      <c r="B13" s="42" t="s">
+      <c r="B13" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C13" s="42" t="s">
+      <c r="C13" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D13" s="42"/>
-      <c r="E13" s="42" t="s">
+      <c r="D13" s="1"/>
+      <c r="E13" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="F13" s="43">
-        <v>5</v>
-      </c>
-      <c r="G13" s="47" t="s">
+      <c r="F13" s="4">
+        <v>5</v>
+      </c>
+      <c r="G13" t="s">
         <v>130</v>
       </c>
-      <c r="H13" s="58">
+      <c r="H13" s="47">
         <v>4</v>
       </c>
-      <c r="I13" s="65">
-        <v>5</v>
-      </c>
-      <c r="J13" s="81">
+      <c r="I13" s="43">
+        <v>5</v>
+      </c>
+      <c r="J13" s="67">
         <v>4</v>
       </c>
-      <c r="K13" s="53">
-        <f t="shared" si="0"/>
+      <c r="K13" s="43">
+        <f t="shared" si="3"/>
         <v>8.5</v>
       </c>
       <c r="L13" s="6">
-        <f>0.25*M13+0.75*N13</f>
+        <f t="shared" si="1"/>
         <v>8.125</v>
       </c>
-      <c r="M13" s="69">
-        <f>(U13+W13)/2</f>
-        <v>10</v>
-      </c>
-      <c r="N13" s="69">
+      <c r="M13" s="56">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="N13" s="56">
         <v>7.5</v>
       </c>
-      <c r="O13" s="69">
-        <f>O12</f>
+      <c r="O13" s="56">
+        <f t="shared" ref="O13:O18" si="5">O12</f>
         <v>6</v>
       </c>
-      <c r="U13" s="44">
-        <v>10</v>
-      </c>
-      <c r="V13" s="44"/>
-      <c r="W13" s="44">
+      <c r="U13" s="5">
+        <v>10</v>
+      </c>
+      <c r="W13" s="5">
         <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="str">
-        <f>_xlfn.CONCAT(B14,"  ",C14)</f>
+        <f t="shared" si="0"/>
         <v>ENZO  BENEDETTO PROENCA</v>
       </c>
       <c r="B14" s="1" t="s">
@@ -4569,32 +4571,32 @@
       <c r="G14" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="H14" s="57">
+      <c r="H14" s="47">
         <v>9</v>
       </c>
-      <c r="I14" s="53">
+      <c r="I14" s="43">
         <v>7</v>
       </c>
-      <c r="J14" s="80">
+      <c r="J14" s="67">
         <v>6</v>
       </c>
-      <c r="K14" s="53">
-        <f t="shared" si="0"/>
+      <c r="K14" s="43">
+        <f t="shared" si="3"/>
         <v>7.5</v>
       </c>
       <c r="L14" s="6">
-        <f>0.25*M14+0.75*N14</f>
+        <f t="shared" si="1"/>
         <v>7.375</v>
       </c>
-      <c r="M14" s="69">
-        <f>(U14+W14)/2</f>
-        <v>10</v>
-      </c>
-      <c r="N14" s="69">
+      <c r="M14" s="56">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="N14" s="56">
         <v>6.5</v>
       </c>
-      <c r="O14" s="69">
-        <f>O13</f>
+      <c r="O14" s="56">
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
       <c r="U14" s="5">
@@ -4606,7 +4608,7 @@
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="str">
-        <f>_xlfn.CONCAT(B15,"  ",C15)</f>
+        <f t="shared" si="0"/>
         <v>FELIPE  VIVIANI SCHULZE</v>
       </c>
       <c r="B15" s="19" t="s">
@@ -4625,39 +4627,39 @@
       <c r="G15" s="21" t="s">
         <v>132</v>
       </c>
-      <c r="H15" s="59">
+      <c r="H15" s="48">
         <v>6</v>
       </c>
-      <c r="I15" s="76">
+      <c r="I15" s="63">
         <v>6.5</v>
       </c>
-      <c r="J15" s="79">
+      <c r="J15" s="66">
         <v>6.5</v>
       </c>
-      <c r="K15" s="54">
-        <f t="shared" si="0"/>
+      <c r="K15" s="44">
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
-      <c r="L15" s="55">
-        <f>0.25*M15+0.75*N15</f>
+      <c r="L15" s="45">
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="M15" s="72">
-        <f>(U15+W15)/2</f>
-        <v>10</v>
-      </c>
-      <c r="N15" s="72">
+      <c r="M15" s="59">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="N15" s="59">
         <v>6</v>
       </c>
-      <c r="O15" s="72">
-        <f>O14</f>
+      <c r="O15" s="59">
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
-      <c r="P15" s="73"/>
-      <c r="Q15" s="59"/>
-      <c r="R15" s="59"/>
-      <c r="S15" s="59"/>
-      <c r="T15" s="62"/>
+      <c r="P15" s="60"/>
+      <c r="Q15" s="48"/>
+      <c r="R15" s="48"/>
+      <c r="S15" s="48"/>
+      <c r="T15" s="50"/>
       <c r="U15" s="22">
         <v>10</v>
       </c>
@@ -4669,7 +4671,7 @@
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="str">
-        <f>_xlfn.CONCAT(B16,"  ",C16)</f>
+        <f t="shared" si="0"/>
         <v>FERNANDO  MATHIAS FERRO DOS SANTOS</v>
       </c>
       <c r="B16" s="1" t="s">
@@ -4688,45 +4690,45 @@
       <c r="G16" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="H16" s="60">
+      <c r="H16" s="49">
         <v>6</v>
       </c>
-      <c r="I16" s="75">
-        <v>5</v>
-      </c>
-      <c r="J16" s="80">
+      <c r="I16" s="62">
+        <v>5</v>
+      </c>
+      <c r="J16" s="67">
         <v>4</v>
       </c>
-      <c r="K16" s="53">
-        <f t="shared" si="0"/>
+      <c r="K16" s="43">
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
       <c r="L16" s="6">
-        <f>0.25*M16+0.75*N16</f>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="M16" s="69">
-        <f>(U16+W16)/2</f>
-        <v>10</v>
-      </c>
-      <c r="N16" s="69">
+      <c r="M16" s="56">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="N16" s="56">
         <v>6</v>
       </c>
-      <c r="O16" s="69">
-        <f>O15</f>
+      <c r="O16" s="56">
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
       <c r="U16" s="11" t="s">
         <v>202</v>
       </c>
       <c r="V16" s="11"/>
-      <c r="W16" s="51" t="s">
+      <c r="W16" s="42" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="str">
-        <f>_xlfn.CONCAT(B17,"  ",C17)</f>
+        <f t="shared" si="0"/>
         <v>FRANCISCO  LOSADA TOTARO</v>
       </c>
       <c r="B17" s="1" t="s">
@@ -4745,32 +4747,32 @@
       <c r="G17" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="H17" s="57">
+      <c r="H17" s="47">
         <v>6</v>
       </c>
-      <c r="I17" s="75">
+      <c r="I17" s="62">
         <v>4.5</v>
       </c>
-      <c r="J17" s="80">
+      <c r="J17" s="67">
         <v>4.5</v>
       </c>
-      <c r="K17" s="53">
-        <f t="shared" si="0"/>
+      <c r="K17" s="43">
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
       <c r="L17" s="6">
-        <f>0.25*M17+0.75*N17</f>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="M17" s="69">
-        <f>(U17+W17)/2</f>
-        <v>10</v>
-      </c>
-      <c r="N17" s="69">
+      <c r="M17" s="56">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="N17" s="56">
         <v>6</v>
       </c>
-      <c r="O17" s="69">
-        <f>O16</f>
+      <c r="O17" s="56">
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
       <c r="U17" s="5">
@@ -4782,7 +4784,7 @@
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="str">
-        <f>_xlfn.CONCAT(B18,"  ",C18)</f>
+        <f t="shared" si="0"/>
         <v>GABRIEL  KEN KAZAMA GERONAZZO</v>
       </c>
       <c r="B18" s="1" t="s">
@@ -4801,32 +4803,32 @@
       <c r="G18" t="s">
         <v>135</v>
       </c>
-      <c r="H18" s="57">
+      <c r="H18" s="47">
         <v>9</v>
       </c>
-      <c r="I18" s="53">
+      <c r="I18" s="43">
         <v>9</v>
       </c>
-      <c r="J18" s="80">
+      <c r="J18" s="67">
         <v>8</v>
       </c>
-      <c r="K18" s="53">
-        <f t="shared" si="0"/>
+      <c r="K18" s="43">
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
       <c r="L18" s="6">
-        <f>0.25*M18+0.75*N18</f>
+        <f t="shared" si="1"/>
         <v>6.75</v>
       </c>
-      <c r="M18" s="69">
-        <f>(U18+W18)/2</f>
+      <c r="M18" s="56">
+        <f t="shared" si="4"/>
         <v>7.5</v>
       </c>
-      <c r="N18" s="69">
+      <c r="N18" s="56">
         <v>6.5</v>
       </c>
-      <c r="O18" s="69">
-        <f>O17</f>
+      <c r="O18" s="56">
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
       <c r="U18" s="5">
@@ -4837,70 +4839,65 @@
       </c>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A19" s="41" t="str">
-        <f>_xlfn.CONCAT(B19,"  ",C19)</f>
+      <c r="A19" s="7" t="str">
+        <f t="shared" si="0"/>
         <v>GABRIEL  LAZARETI CARDOSO</v>
       </c>
-      <c r="B19" s="42" t="s">
+      <c r="B19" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C19" s="42" t="s">
+      <c r="C19" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D19" s="42"/>
-      <c r="E19" s="42" t="s">
+      <c r="D19" s="1"/>
+      <c r="E19" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="F19" s="43"/>
       <c r="G19" s="14"/>
-      <c r="H19" s="58">
+      <c r="H19" s="47">
         <v>8</v>
       </c>
-      <c r="I19" s="65" t="s">
+      <c r="I19" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="J19" s="81"/>
-      <c r="K19" s="53">
-        <f t="shared" si="0"/>
+      <c r="K19" s="43">
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="L19" s="6">
-        <f>0.25*M19+0.75*N19</f>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="M19" s="69">
-        <f>(U19+W19)/2</f>
+      <c r="M19" s="56">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N19" s="69">
+      <c r="N19" s="56">
         <v>8</v>
       </c>
-      <c r="O19" s="69">
+      <c r="O19" s="56">
         <f>SUM(Q19,R19,S19)</f>
         <v>8</v>
       </c>
-      <c r="P19" s="70" t="s">
+      <c r="P19" s="57" t="s">
         <v>195</v>
       </c>
-      <c r="Q19" s="57">
+      <c r="Q19" s="47">
         <v>2.5</v>
       </c>
-      <c r="R19" s="57">
+      <c r="R19" s="47">
         <v>3</v>
       </c>
-      <c r="S19" s="57">
+      <c r="S19" s="47">
         <v>2.5</v>
       </c>
-      <c r="T19" s="63" t="s">
+      <c r="T19" s="51" t="s">
         <v>199</v>
       </c>
-      <c r="U19" s="44"/>
-      <c r="V19" s="44"/>
-      <c r="W19" s="44"/>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" s="18" t="str">
-        <f>_xlfn.CONCAT(B20,"  ",C20)</f>
+        <f t="shared" si="0"/>
         <v>GABRIEL  TORTOLIO FONSECA</v>
       </c>
       <c r="B20" s="19" t="s">
@@ -4915,39 +4912,39 @@
       </c>
       <c r="F20" s="20"/>
       <c r="G20" s="21"/>
-      <c r="H20" s="59">
+      <c r="H20" s="48">
         <v>1</v>
       </c>
-      <c r="I20" s="54">
+      <c r="I20" s="44">
         <v>4</v>
       </c>
-      <c r="J20" s="79">
+      <c r="J20" s="66">
         <v>3</v>
       </c>
-      <c r="K20" s="54">
-        <f t="shared" si="0"/>
+      <c r="K20" s="44">
+        <f t="shared" si="3"/>
         <v>8.5</v>
       </c>
-      <c r="L20" s="55">
-        <f>0.25*M20+0.75*N20</f>
+      <c r="L20" s="45">
+        <f t="shared" si="1"/>
         <v>8.375</v>
       </c>
-      <c r="M20" s="72">
-        <f>(U20+W20)/2</f>
+      <c r="M20" s="59">
+        <f t="shared" si="4"/>
         <v>3.5</v>
       </c>
-      <c r="N20" s="72">
-        <v>10</v>
-      </c>
-      <c r="O20" s="72">
+      <c r="N20" s="59">
+        <v>10</v>
+      </c>
+      <c r="O20" s="59">
         <f>O19</f>
         <v>8</v>
       </c>
-      <c r="P20" s="73"/>
-      <c r="Q20" s="59"/>
-      <c r="R20" s="59"/>
-      <c r="S20" s="59"/>
-      <c r="T20" s="62"/>
+      <c r="P20" s="60"/>
+      <c r="Q20" s="48"/>
+      <c r="R20" s="48"/>
+      <c r="S20" s="48"/>
+      <c r="T20" s="50"/>
       <c r="U20" s="22">
         <v>7</v>
       </c>
@@ -4958,65 +4955,65 @@
       <c r="X20" s="33"/>
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A21" s="41" t="str">
-        <f>_xlfn.CONCAT(B21,"  ",C21)</f>
+      <c r="A21" s="7" t="str">
+        <f t="shared" si="0"/>
         <v>GIOVANA  SIMOES FRANCO</v>
       </c>
-      <c r="B21" s="42" t="s">
+      <c r="B21" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="C21" s="42" t="s">
+      <c r="C21" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="D21" s="45"/>
-      <c r="E21" s="42" t="s">
+      <c r="D21" s="9"/>
+      <c r="E21" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="F21" s="46">
+      <c r="F21" s="10">
         <v>3</v>
       </c>
-      <c r="G21" s="42" t="s">
+      <c r="G21" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="H21" s="61">
+      <c r="H21" s="49">
         <v>3</v>
       </c>
-      <c r="I21" s="65">
+      <c r="I21" s="43">
         <v>7</v>
       </c>
-      <c r="J21" s="81">
+      <c r="J21" s="67">
         <v>6</v>
       </c>
-      <c r="K21" s="53">
-        <f t="shared" si="0"/>
+      <c r="K21" s="43">
+        <f t="shared" si="3"/>
         <v>9.5</v>
       </c>
       <c r="L21" s="6">
-        <f>0.25*M21+0.75*N21</f>
+        <f t="shared" si="1"/>
         <v>9.25</v>
       </c>
-      <c r="M21" s="69">
-        <f>(U21+W21)/2</f>
-        <v>10</v>
-      </c>
-      <c r="N21" s="69">
+      <c r="M21" s="56">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="N21" s="56">
         <v>9</v>
       </c>
-      <c r="O21" s="69">
+      <c r="O21" s="56">
         <f>O20</f>
         <v>8</v>
       </c>
-      <c r="U21" s="48" t="s">
+      <c r="U21" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="V21" s="48"/>
-      <c r="W21" s="52" t="s">
+      <c r="V21" s="11"/>
+      <c r="W21" s="42" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="str">
-        <f>_xlfn.CONCAT(B22,"  ",C22)</f>
+        <f t="shared" si="0"/>
         <v>GUILHERME  FERREIRA MARTINS RAMOS</v>
       </c>
       <c r="B22" s="1" t="s">
@@ -5035,31 +5032,31 @@
       <c r="G22" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="H22" s="57">
+      <c r="H22" s="47">
         <v>6</v>
       </c>
-      <c r="I22" s="53">
+      <c r="I22" s="43">
         <v>8</v>
       </c>
-      <c r="J22" s="80">
+      <c r="J22" s="67">
         <v>7</v>
       </c>
-      <c r="K22" s="53">
-        <f t="shared" si="0"/>
+      <c r="K22" s="43">
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="L22" s="6">
-        <f>0.25*M22+0.75*N22</f>
+        <f t="shared" si="1"/>
         <v>5.75</v>
       </c>
-      <c r="M22" s="69">
-        <f>(U22+W22)/2</f>
-        <v>5</v>
-      </c>
-      <c r="N22" s="69">
+      <c r="M22" s="56">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="N22" s="56">
         <v>6</v>
       </c>
-      <c r="O22" s="69">
+      <c r="O22" s="56">
         <f>O21</f>
         <v>8</v>
       </c>
@@ -5069,7 +5066,7 @@
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="str">
-        <f>_xlfn.CONCAT(B23,"  ",C23)</f>
+        <f t="shared" si="0"/>
         <v>GUSTAVO  KENZO NAKAZATO SLEIMAN</v>
       </c>
       <c r="B23" s="1" t="s">
@@ -5082,25 +5079,25 @@
       <c r="E23" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="I23" s="53" t="s">
+      <c r="I23" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="K23" s="53">
-        <f t="shared" si="0"/>
+      <c r="K23" s="43">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L23" s="6">
-        <f>0.25*M23+0.75*N23</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="M23" s="69">
-        <f>(U23+W23)/2</f>
+      <c r="M23" s="56">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="str">
-        <f>_xlfn.CONCAT(B24,"  ",C24)</f>
+        <f t="shared" si="0"/>
         <v>HENRIQUE  YUJI ISOGAI YONEOKA</v>
       </c>
       <c r="B24" s="1" t="s">
@@ -5119,45 +5116,45 @@
       <c r="G24" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="H24" s="57">
+      <c r="H24" s="47">
         <v>7</v>
       </c>
-      <c r="I24" s="75">
+      <c r="I24" s="62">
         <v>4</v>
       </c>
-      <c r="J24" s="80">
+      <c r="J24" s="67">
         <v>4</v>
       </c>
-      <c r="K24" s="53">
-        <f t="shared" si="0"/>
+      <c r="K24" s="43">
+        <f t="shared" si="3"/>
         <v>6.5</v>
       </c>
       <c r="L24" s="6">
-        <f>0.25*M24+0.75*N24</f>
+        <f t="shared" si="1"/>
         <v>6.125</v>
       </c>
-      <c r="M24" s="69">
-        <f>(U24+W24)/2</f>
+      <c r="M24" s="56">
+        <f t="shared" si="4"/>
         <v>3.5</v>
       </c>
-      <c r="N24" s="69">
+      <c r="N24" s="56">
         <v>7</v>
       </c>
-      <c r="O24" s="69">
-        <f>O23</f>
+      <c r="O24" s="56">
+        <f t="shared" ref="O24:O31" si="6">O23</f>
         <v>0</v>
       </c>
       <c r="U24" s="5">
         <v>7</v>
       </c>
-      <c r="V24" s="50" t="s">
+      <c r="V24" s="41" t="s">
         <v>204</v>
       </c>
-      <c r="W24" s="50"/>
+      <c r="W24" s="41"/>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A25" s="18" t="str">
-        <f>_xlfn.CONCAT(B25,"  ",C25)</f>
+        <f t="shared" si="0"/>
         <v>ISMAEL  DE SOUSA SILVA</v>
       </c>
       <c r="B25" s="19" t="s">
@@ -5176,39 +5173,39 @@
       <c r="G25" s="21" t="s">
         <v>139</v>
       </c>
-      <c r="H25" s="59">
+      <c r="H25" s="48">
         <v>4</v>
       </c>
-      <c r="I25" s="54">
+      <c r="I25" s="44">
         <v>6</v>
       </c>
-      <c r="J25" s="79">
-        <v>5</v>
-      </c>
-      <c r="K25" s="54">
-        <f t="shared" si="0"/>
+      <c r="J25" s="66">
+        <v>5</v>
+      </c>
+      <c r="K25" s="44">
+        <f t="shared" si="3"/>
         <v>8.5</v>
       </c>
-      <c r="L25" s="55">
-        <f>0.25*M25+0.75*N25</f>
+      <c r="L25" s="45">
+        <f t="shared" si="1"/>
         <v>8.125</v>
       </c>
-      <c r="M25" s="72">
-        <f>(U25+W25)/2</f>
-        <v>10</v>
-      </c>
-      <c r="N25" s="72">
+      <c r="M25" s="59">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="N25" s="59">
         <v>7.5</v>
       </c>
-      <c r="O25" s="72">
-        <f>O24</f>
+      <c r="O25" s="59">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="P25" s="73"/>
-      <c r="Q25" s="59"/>
-      <c r="R25" s="59"/>
-      <c r="S25" s="59"/>
-      <c r="T25" s="62"/>
+      <c r="P25" s="60"/>
+      <c r="Q25" s="48"/>
+      <c r="R25" s="48"/>
+      <c r="S25" s="48"/>
+      <c r="T25" s="50"/>
       <c r="U25" s="22">
         <v>10</v>
       </c>
@@ -5220,7 +5217,7 @@
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="str">
-        <f>_xlfn.CONCAT(B26,"  ",C26)</f>
+        <f t="shared" si="0"/>
         <v>JESSICA  DOS SANTOS SANTANA BISPO</v>
       </c>
       <c r="B26" s="1" t="s">
@@ -5239,45 +5236,45 @@
       <c r="G26" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="H26" s="60">
+      <c r="H26" s="49">
         <v>9</v>
       </c>
-      <c r="I26" s="53">
+      <c r="I26" s="43">
         <v>5.5</v>
       </c>
-      <c r="J26" s="80">
+      <c r="J26" s="67">
         <v>4.5</v>
       </c>
-      <c r="K26" s="53">
-        <f t="shared" si="0"/>
+      <c r="K26" s="43">
+        <f t="shared" si="3"/>
         <v>7.5</v>
       </c>
       <c r="L26" s="6">
-        <f>0.25*M26+0.75*N26</f>
+        <f t="shared" si="1"/>
         <v>7.375</v>
       </c>
-      <c r="M26" s="69">
-        <f>(U26+W26)/2</f>
-        <v>10</v>
-      </c>
-      <c r="N26" s="69">
+      <c r="M26" s="56">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="N26" s="56">
         <v>6.5</v>
       </c>
-      <c r="O26" s="69">
-        <f>O25</f>
+      <c r="O26" s="56">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="U26" s="11" t="s">
         <v>202</v>
       </c>
       <c r="V26" s="11"/>
-      <c r="W26" s="51" t="s">
+      <c r="W26" s="42" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="str">
-        <f>_xlfn.CONCAT(B27,"  ",C27)</f>
+        <f t="shared" si="0"/>
         <v>JOAO  ROCHA MURGEL</v>
       </c>
       <c r="B27" s="1" t="s">
@@ -5291,26 +5288,26 @@
         <v>94</v>
       </c>
       <c r="G27" s="14"/>
-      <c r="H27" s="57">
+      <c r="H27" s="47">
         <v>8</v>
       </c>
-      <c r="K27" s="53">
-        <f t="shared" si="0"/>
+      <c r="K27" s="43">
+        <f t="shared" si="3"/>
         <v>7.5</v>
       </c>
       <c r="L27" s="6">
-        <f>0.25*M27+0.75*N27</f>
+        <f t="shared" si="1"/>
         <v>7.25</v>
       </c>
-      <c r="M27" s="69">
-        <f>(U27+W27)/2</f>
-        <v>5</v>
-      </c>
-      <c r="N27" s="69">
+      <c r="M27" s="56">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="N27" s="56">
         <v>8</v>
       </c>
-      <c r="O27" s="69">
-        <f>O26</f>
+      <c r="O27" s="56">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="U27" s="5">
@@ -5319,7 +5316,7 @@
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="str">
-        <f>_xlfn.CONCAT(B28,"  ",C28)</f>
+        <f t="shared" si="0"/>
         <v>JOAO  VICTOR MARTINS</v>
       </c>
       <c r="B28" s="1" t="s">
@@ -5332,32 +5329,32 @@
       <c r="E28" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="H28" s="57">
+      <c r="H28" s="47">
         <v>7</v>
       </c>
-      <c r="I28" s="75">
+      <c r="I28" s="62">
         <v>5.5</v>
       </c>
-      <c r="J28" s="80">
+      <c r="J28" s="67">
         <v>5.5</v>
       </c>
-      <c r="K28" s="53">
-        <f t="shared" si="0"/>
+      <c r="K28" s="43">
+        <f t="shared" si="3"/>
         <v>6.5</v>
       </c>
       <c r="L28" s="6">
-        <f>0.25*M28+0.75*N28</f>
+        <f t="shared" si="1"/>
         <v>6.5</v>
       </c>
-      <c r="M28" s="69">
-        <f>(U28+W28)/2</f>
-        <v>5</v>
-      </c>
-      <c r="N28" s="69">
+      <c r="M28" s="56">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="N28" s="56">
         <v>7</v>
       </c>
-      <c r="O28" s="69">
-        <f>O27</f>
+      <c r="O28" s="56">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="U28" s="5">
@@ -5366,7 +5363,7 @@
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="str">
-        <f>_xlfn.CONCAT(B29,"  ",C29)</f>
+        <f t="shared" si="0"/>
         <v>JULIA  SANTOS OLIVEIRA</v>
       </c>
       <c r="B29" s="1" t="s">
@@ -5385,32 +5382,32 @@
       <c r="G29" s="14" t="s">
         <v>147</v>
       </c>
-      <c r="H29" s="57">
+      <c r="H29" s="47">
         <v>3</v>
       </c>
-      <c r="I29" s="53">
+      <c r="I29" s="43">
         <v>6.5</v>
       </c>
-      <c r="J29" s="80">
+      <c r="J29" s="67">
         <v>5.5</v>
       </c>
-      <c r="K29" s="53">
-        <f t="shared" si="0"/>
+      <c r="K29" s="43">
+        <f t="shared" si="3"/>
         <v>9.5</v>
       </c>
       <c r="L29" s="6">
-        <f>0.25*M29+0.75*N29</f>
+        <f t="shared" si="1"/>
         <v>9.25</v>
       </c>
-      <c r="M29" s="69">
-        <f>(U29+W29)/2</f>
-        <v>10</v>
-      </c>
-      <c r="N29" s="69">
+      <c r="M29" s="56">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="N29" s="56">
         <v>9</v>
       </c>
-      <c r="O29" s="69">
-        <f>O28</f>
+      <c r="O29" s="56">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="U29" s="5">
@@ -5422,7 +5419,7 @@
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A30" s="18" t="str">
-        <f>_xlfn.CONCAT(B30,"  ",C30)</f>
+        <f t="shared" si="0"/>
         <v>LARISSA  YURI SATO</v>
       </c>
       <c r="B30" s="19" t="s">
@@ -5441,39 +5438,39 @@
       <c r="G30" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="H30" s="59">
+      <c r="H30" s="48">
         <v>3</v>
       </c>
-      <c r="I30" s="54">
+      <c r="I30" s="44">
         <v>7</v>
       </c>
-      <c r="J30" s="79">
+      <c r="J30" s="66">
         <v>6</v>
       </c>
-      <c r="K30" s="54">
-        <f t="shared" si="0"/>
+      <c r="K30" s="44">
+        <f t="shared" si="3"/>
         <v>9.5</v>
       </c>
-      <c r="L30" s="55">
-        <f>0.25*M30+0.75*N30</f>
+      <c r="L30" s="45">
+        <f t="shared" si="1"/>
         <v>9.25</v>
       </c>
-      <c r="M30" s="72">
-        <f>(U30+W30)/2</f>
-        <v>10</v>
-      </c>
-      <c r="N30" s="72">
+      <c r="M30" s="59">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="N30" s="59">
         <v>9</v>
       </c>
-      <c r="O30" s="72">
-        <f>O29</f>
+      <c r="O30" s="59">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="P30" s="73"/>
-      <c r="Q30" s="59"/>
-      <c r="R30" s="59"/>
-      <c r="S30" s="59"/>
-      <c r="T30" s="62"/>
+      <c r="P30" s="60"/>
+      <c r="Q30" s="48"/>
+      <c r="R30" s="48"/>
+      <c r="S30" s="48"/>
+      <c r="T30" s="50"/>
       <c r="U30" s="22">
         <v>10</v>
       </c>
@@ -5485,7 +5482,7 @@
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="str">
-        <f>_xlfn.CONCAT(B31,"  ",C31)</f>
+        <f t="shared" si="0"/>
         <v>LEONARDO  PATRIANI CARDOSO</v>
       </c>
       <c r="B31" s="1" t="s">
@@ -5500,32 +5497,32 @@
       </c>
       <c r="F31" s="10"/>
       <c r="G31" s="1"/>
-      <c r="H31" s="60">
+      <c r="H31" s="49">
         <v>7</v>
       </c>
-      <c r="I31" s="53">
+      <c r="I31" s="43">
         <v>7.5</v>
       </c>
-      <c r="J31" s="80">
+      <c r="J31" s="67">
         <v>6.5</v>
       </c>
-      <c r="K31" s="53">
-        <f t="shared" si="0"/>
+      <c r="K31" s="43">
+        <f t="shared" si="3"/>
         <v>5.5</v>
       </c>
       <c r="L31" s="6">
-        <f>0.25*M31+0.75*N31</f>
+        <f t="shared" si="1"/>
         <v>5.25</v>
       </c>
-      <c r="M31" s="69">
-        <f>(U31+W31)/2</f>
+      <c r="M31" s="56">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N31" s="69">
+      <c r="N31" s="56">
         <v>7</v>
       </c>
-      <c r="O31" s="69">
-        <f>O30</f>
+      <c r="O31" s="56">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="U31" s="11"/>
@@ -5533,107 +5530,102 @@
       <c r="W31" s="11"/>
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A32" s="41" t="str">
-        <f>_xlfn.CONCAT(B32,"  ",C32)</f>
+      <c r="A32" s="7" t="str">
+        <f t="shared" si="0"/>
         <v>LIVIA  CANTOWITZ</v>
       </c>
-      <c r="B32" s="42" t="s">
+      <c r="B32" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C32" s="42" t="s">
+      <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D32" s="45"/>
-      <c r="E32" s="42" t="s">
+      <c r="D32" s="9"/>
+      <c r="E32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F32" s="43"/>
       <c r="G32" s="14"/>
-      <c r="H32" s="58"/>
-      <c r="I32" s="65">
-        <v>5</v>
-      </c>
-      <c r="J32" s="81">
+      <c r="I32" s="43">
+        <v>5</v>
+      </c>
+      <c r="J32" s="67">
         <v>4</v>
       </c>
-      <c r="K32" s="53">
-        <f t="shared" si="0"/>
+      <c r="K32" s="43">
+        <f t="shared" si="3"/>
         <v>1.5</v>
       </c>
       <c r="L32" s="6">
-        <f>0.25*M32+0.75*N32</f>
+        <f t="shared" si="1"/>
         <v>1.25</v>
       </c>
-      <c r="M32" s="69">
-        <f>(U32+W32)/2</f>
-        <v>5</v>
-      </c>
-      <c r="U32" s="44">
-        <v>10</v>
-      </c>
-      <c r="V32" s="44"/>
-      <c r="W32" s="44"/>
+      <c r="M32" s="56">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="U32" s="5">
+        <v>10</v>
+      </c>
     </row>
     <row r="33" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A33" s="41" t="str">
-        <f>_xlfn.CONCAT(B33,"  ",C33)</f>
+      <c r="A33" s="7" t="str">
+        <f t="shared" si="0"/>
         <v>LUCAS  PIRES DE CAMARGO SARAI</v>
       </c>
-      <c r="B33" s="42" t="s">
+      <c r="B33" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="C33" s="42" t="s">
+      <c r="C33" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D33" s="42"/>
-      <c r="E33" s="42" t="s">
+      <c r="D33" s="1"/>
+      <c r="E33" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="F33" s="43">
-        <v>5</v>
-      </c>
-      <c r="G33" s="47" t="s">
+      <c r="F33" s="4">
+        <v>5</v>
+      </c>
+      <c r="G33" t="s">
         <v>142</v>
       </c>
-      <c r="H33" s="58">
+      <c r="H33" s="47">
         <v>9</v>
       </c>
-      <c r="I33" s="65">
+      <c r="I33" s="43">
         <v>11</v>
       </c>
-      <c r="J33" s="81">
-        <v>10</v>
-      </c>
-      <c r="K33" s="53">
-        <f t="shared" si="0"/>
+      <c r="J33" s="67">
+        <v>10</v>
+      </c>
+      <c r="K33" s="43">
+        <f t="shared" si="3"/>
         <v>7.5</v>
       </c>
       <c r="L33" s="6">
-        <f>0.25*M33+0.75*N33</f>
+        <f t="shared" si="1"/>
         <v>7.375</v>
       </c>
-      <c r="M33" s="69">
-        <f>(U33+W33)/2</f>
-        <v>10</v>
-      </c>
-      <c r="N33" s="69">
+      <c r="M33" s="56">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="N33" s="56">
         <v>6.5</v>
       </c>
-      <c r="O33" s="69">
+      <c r="O33" s="56">
         <f>O32</f>
         <v>0</v>
       </c>
-      <c r="U33" s="44">
-        <v>10</v>
-      </c>
-      <c r="V33" s="44"/>
-      <c r="W33" s="44">
+      <c r="U33" s="5">
+        <v>10</v>
+      </c>
+      <c r="W33" s="5">
         <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="str">
-        <f>_xlfn.CONCAT(B34,"  ",C34)</f>
+        <f t="shared" si="0"/>
         <v>MARCO  ANTONIO DE CAMARGO</v>
       </c>
       <c r="B34" s="1" t="s">
@@ -5652,31 +5644,31 @@
       <c r="G34" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="H34" s="57">
+      <c r="H34" s="47">
         <v>1</v>
       </c>
-      <c r="I34" s="53">
+      <c r="I34" s="43">
         <v>7</v>
       </c>
-      <c r="J34" s="80">
+      <c r="J34" s="67">
         <v>6</v>
       </c>
-      <c r="K34" s="53">
-        <f t="shared" si="0"/>
+      <c r="K34" s="43">
+        <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="L34" s="6">
-        <f>0.25*M34+0.75*N34</f>
+        <f t="shared" si="1"/>
         <v>9.875</v>
       </c>
-      <c r="M34" s="69">
-        <f>(U34+W34)/2</f>
+      <c r="M34" s="56">
+        <f t="shared" si="4"/>
         <v>9.5</v>
       </c>
-      <c r="N34" s="69">
-        <v>10</v>
-      </c>
-      <c r="O34" s="69">
+      <c r="N34" s="56">
+        <v>10</v>
+      </c>
+      <c r="O34" s="56">
         <f>O33</f>
         <v>0</v>
       </c>
@@ -5689,7 +5681,7 @@
     </row>
     <row r="35" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A35" s="18" t="str">
-        <f>_xlfn.CONCAT(B35,"  ",C35)</f>
+        <f t="shared" si="0"/>
         <v>MARINA  BARROCA</v>
       </c>
       <c r="B35" s="19" t="s">
@@ -5708,47 +5700,47 @@
       <c r="G35" s="21" t="s">
         <v>148</v>
       </c>
-      <c r="H35" s="59">
-        <v>10</v>
-      </c>
-      <c r="I35" s="76">
+      <c r="H35" s="48">
+        <v>10</v>
+      </c>
+      <c r="I35" s="63">
         <v>4.5</v>
       </c>
-      <c r="J35" s="79">
+      <c r="J35" s="66">
         <v>4.5</v>
       </c>
-      <c r="K35" s="54">
-        <f t="shared" si="0"/>
+      <c r="K35" s="44">
+        <f t="shared" si="3"/>
         <v>7.5</v>
       </c>
-      <c r="L35" s="55">
-        <f>0.25*M35+0.75*N35</f>
+      <c r="L35" s="45">
+        <f t="shared" si="1"/>
         <v>7.375</v>
       </c>
-      <c r="M35" s="72">
-        <f>(U35+W35)/2</f>
-        <v>10</v>
-      </c>
-      <c r="N35" s="72">
+      <c r="M35" s="59">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="N35" s="59">
         <v>6.5</v>
       </c>
-      <c r="O35" s="72">
+      <c r="O35" s="59">
         <f>SUM(Q35,R35,S35)</f>
         <v>6.5</v>
       </c>
-      <c r="P35" s="73" t="s">
+      <c r="P35" s="60" t="s">
         <v>190</v>
       </c>
-      <c r="Q35" s="59">
+      <c r="Q35" s="48">
         <v>1.5</v>
       </c>
-      <c r="R35" s="59">
+      <c r="R35" s="48">
         <v>2.5</v>
       </c>
-      <c r="S35" s="59">
+      <c r="S35" s="48">
         <v>2.5</v>
       </c>
-      <c r="T35" s="62"/>
+      <c r="T35" s="50"/>
       <c r="U35" s="22">
         <v>10</v>
       </c>
@@ -5760,7 +5752,7 @@
     </row>
     <row r="36" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="str">
-        <f>_xlfn.CONCAT(B36,"  ",C36)</f>
+        <f t="shared" si="0"/>
         <v>MATHEUS  HENRIQUE DE OLIVEIRA SANTOS</v>
       </c>
       <c r="B36" s="1" t="s">
@@ -5775,32 +5767,32 @@
       </c>
       <c r="F36" s="10"/>
       <c r="G36" s="1"/>
-      <c r="H36" s="60">
-        <v>10</v>
-      </c>
-      <c r="I36" s="53">
+      <c r="H36" s="49">
+        <v>10</v>
+      </c>
+      <c r="I36" s="43">
         <v>4</v>
       </c>
-      <c r="J36" s="80">
+      <c r="J36" s="67">
         <v>3</v>
       </c>
-      <c r="K36" s="53">
-        <f t="shared" si="0"/>
+      <c r="K36" s="43">
+        <f t="shared" si="3"/>
         <v>6.5</v>
       </c>
       <c r="L36" s="6">
-        <f>0.25*M36+0.75*N36</f>
+        <f t="shared" si="1"/>
         <v>6.125</v>
       </c>
-      <c r="M36" s="69">
-        <f>(U36+W36)/2</f>
-        <v>5</v>
-      </c>
-      <c r="N36" s="69">
+      <c r="M36" s="56">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="N36" s="56">
         <v>6.5</v>
       </c>
-      <c r="O36" s="69">
-        <f>O35</f>
+      <c r="O36" s="56">
+        <f t="shared" ref="O36:O42" si="7">O35</f>
         <v>6.5</v>
       </c>
       <c r="U36" s="11" t="s">
@@ -5810,57 +5802,54 @@
       <c r="W36" s="11"/>
     </row>
     <row r="37" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A37" s="41" t="str">
-        <f>_xlfn.CONCAT(B37,"  ",C37)</f>
+      <c r="A37" s="7" t="str">
+        <f t="shared" si="0"/>
         <v>NATAN  MOREIRA PASSOS</v>
       </c>
-      <c r="B37" s="42" t="s">
+      <c r="B37" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C37" s="42" t="s">
+      <c r="C37" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="D37" s="45"/>
-      <c r="E37" s="42" t="s">
+      <c r="D37" s="9"/>
+      <c r="E37" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="F37" s="43"/>
       <c r="G37" s="14"/>
-      <c r="H37" s="58">
+      <c r="H37" s="47">
         <v>1</v>
       </c>
-      <c r="I37" s="65"/>
-      <c r="J37" s="81"/>
-      <c r="K37" s="53">
-        <f t="shared" si="0"/>
+      <c r="K37" s="43">
+        <f t="shared" si="3"/>
         <v>8.5</v>
       </c>
       <c r="L37" s="6">
-        <f>0.25*M37+0.75*N37</f>
+        <f t="shared" si="1"/>
         <v>8.375</v>
       </c>
-      <c r="M37" s="69">
-        <f>(U37+W37)/2</f>
+      <c r="M37" s="56">
+        <f t="shared" si="4"/>
         <v>3.5</v>
       </c>
-      <c r="N37" s="69">
-        <v>10</v>
-      </c>
-      <c r="O37" s="69">
-        <f>O36</f>
+      <c r="N37" s="56">
+        <v>10</v>
+      </c>
+      <c r="O37" s="56">
+        <f t="shared" si="7"/>
         <v>6.5</v>
       </c>
-      <c r="U37" s="44">
+      <c r="U37" s="5">
         <v>7</v>
       </c>
-      <c r="V37" s="49" t="s">
+      <c r="V37" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="W37" s="49"/>
+      <c r="W37" s="41"/>
     </row>
     <row r="38" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="str">
-        <f>_xlfn.CONCAT(B38,"  ",C38)</f>
+        <f t="shared" si="0"/>
         <v>NICOLAS  HENRIQUES DE ALMEIDA</v>
       </c>
       <c r="B38" s="1" t="s">
@@ -5879,32 +5868,32 @@
       <c r="G38" t="s">
         <v>144</v>
       </c>
-      <c r="H38" s="57">
+      <c r="H38" s="47">
         <v>1</v>
       </c>
-      <c r="I38" s="53">
+      <c r="I38" s="43">
         <v>7.5</v>
       </c>
-      <c r="J38" s="80">
+      <c r="J38" s="67">
         <v>6.5</v>
       </c>
-      <c r="K38" s="53">
-        <f t="shared" si="0"/>
+      <c r="K38" s="43">
+        <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="L38" s="6">
-        <f>0.25*M38+0.75*N38</f>
-        <v>10</v>
-      </c>
-      <c r="M38" s="69">
-        <f>(U38+W38)/2</f>
-        <v>10</v>
-      </c>
-      <c r="N38" s="69">
-        <v>10</v>
-      </c>
-      <c r="O38" s="69">
-        <f>O37</f>
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="M38" s="56">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="N38" s="56">
+        <v>10</v>
+      </c>
+      <c r="O38" s="56">
+        <f t="shared" si="7"/>
         <v>6.5</v>
       </c>
       <c r="U38" s="5">
@@ -5916,7 +5905,7 @@
     </row>
     <row r="39" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="str">
-        <f>_xlfn.CONCAT(B39,"  ",C39)</f>
+        <f t="shared" si="0"/>
         <v>OTAVIO  AUGUSTO FREIRE DE ANDRADE BRUZADI</v>
       </c>
       <c r="B39" s="1" t="s">
@@ -5935,32 +5924,32 @@
       <c r="G39" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="H39" s="57">
+      <c r="H39" s="47">
         <v>9</v>
       </c>
-      <c r="I39" s="53">
+      <c r="I39" s="43">
         <v>7.5</v>
       </c>
-      <c r="J39" s="80">
+      <c r="J39" s="67">
         <v>6.5</v>
       </c>
-      <c r="K39" s="53">
-        <f t="shared" si="0"/>
+      <c r="K39" s="43">
+        <f t="shared" si="3"/>
         <v>7.5</v>
       </c>
       <c r="L39" s="6">
-        <f>0.25*M39+0.75*N39</f>
+        <f t="shared" si="1"/>
         <v>7.375</v>
       </c>
-      <c r="M39" s="69">
-        <f>(U39+W39)/2</f>
-        <v>10</v>
-      </c>
-      <c r="N39" s="69">
+      <c r="M39" s="56">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="N39" s="56">
         <v>6.5</v>
       </c>
-      <c r="O39" s="69">
-        <f>O38</f>
+      <c r="O39" s="56">
+        <f t="shared" si="7"/>
         <v>6.5</v>
       </c>
       <c r="U39" s="5">
@@ -5972,7 +5961,7 @@
     </row>
     <row r="40" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A40" s="18" t="str">
-        <f>_xlfn.CONCAT(B40,"  ",C40)</f>
+        <f t="shared" si="0"/>
         <v>THOMAS  PINHEIRO GRANDIN</v>
       </c>
       <c r="B40" s="19" t="s">
@@ -5987,39 +5976,39 @@
       </c>
       <c r="F40" s="20"/>
       <c r="G40" s="21"/>
-      <c r="H40" s="59">
+      <c r="H40" s="48">
         <v>1</v>
       </c>
-      <c r="I40" s="54">
+      <c r="I40" s="44">
         <v>5.5</v>
       </c>
-      <c r="J40" s="79">
+      <c r="J40" s="66">
         <v>4.5</v>
       </c>
-      <c r="K40" s="54">
-        <f t="shared" si="0"/>
+      <c r="K40" s="44">
+        <f t="shared" si="3"/>
         <v>7.5</v>
       </c>
-      <c r="L40" s="55">
-        <f>0.25*M40+0.75*N40</f>
+      <c r="L40" s="45">
+        <f t="shared" si="1"/>
         <v>7.5</v>
       </c>
-      <c r="M40" s="72">
-        <f>(U40+W40)/2</f>
+      <c r="M40" s="59">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N40" s="72">
-        <v>10</v>
-      </c>
-      <c r="O40" s="72">
-        <f>O39</f>
+      <c r="N40" s="59">
+        <v>10</v>
+      </c>
+      <c r="O40" s="59">
+        <f t="shared" si="7"/>
         <v>6.5</v>
       </c>
-      <c r="P40" s="73"/>
-      <c r="Q40" s="59"/>
-      <c r="R40" s="59"/>
-      <c r="S40" s="59"/>
-      <c r="T40" s="62"/>
+      <c r="P40" s="60"/>
+      <c r="Q40" s="48"/>
+      <c r="R40" s="48"/>
+      <c r="S40" s="48"/>
+      <c r="T40" s="50"/>
       <c r="U40" s="22"/>
       <c r="V40" s="22"/>
       <c r="W40" s="22"/>
@@ -6027,7 +6016,7 @@
     </row>
     <row r="41" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="str">
-        <f>_xlfn.CONCAT(B41,"  ",C41)</f>
+        <f t="shared" si="0"/>
         <v>TIAGO  SILVEIRA LOPES</v>
       </c>
       <c r="B41" s="1" t="s">
@@ -6046,32 +6035,32 @@
       <c r="G41" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="H41" s="57">
+      <c r="H41" s="47">
         <v>6</v>
       </c>
-      <c r="I41" s="75">
+      <c r="I41" s="62">
         <v>4</v>
       </c>
-      <c r="J41" s="80">
+      <c r="J41" s="67">
         <v>4</v>
       </c>
-      <c r="K41" s="53">
-        <f t="shared" si="0"/>
+      <c r="K41" s="43">
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="L41" s="6">
-        <f>0.25*M41+0.75*N41</f>
+        <f t="shared" si="1"/>
         <v>5.75</v>
       </c>
-      <c r="M41" s="69">
-        <f>(U41+W41)/2</f>
-        <v>5</v>
-      </c>
-      <c r="N41" s="69">
+      <c r="M41" s="56">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="N41" s="56">
         <v>6</v>
       </c>
-      <c r="O41" s="69">
-        <f>O40</f>
+      <c r="O41" s="56">
+        <f t="shared" si="7"/>
         <v>6.5</v>
       </c>
       <c r="U41" s="5">
@@ -6080,7 +6069,7 @@
     </row>
     <row r="42" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A42" s="18" t="str">
-        <f>_xlfn.CONCAT(B42,"  ",C42)</f>
+        <f t="shared" si="0"/>
         <v>VITOR  ALVES PEREIRA</v>
       </c>
       <c r="B42" s="19" t="s">
@@ -6099,39 +6088,39 @@
       <c r="G42" s="21" t="s">
         <v>146</v>
       </c>
-      <c r="H42" s="59">
+      <c r="H42" s="48">
         <v>4</v>
       </c>
-      <c r="I42" s="54">
+      <c r="I42" s="44">
         <v>4</v>
       </c>
-      <c r="J42" s="79">
+      <c r="J42" s="66">
         <v>3</v>
       </c>
-      <c r="K42" s="54">
-        <f t="shared" si="0"/>
+      <c r="K42" s="44">
+        <f t="shared" si="3"/>
         <v>8.5</v>
       </c>
-      <c r="L42" s="55">
-        <f>0.25*M42+0.75*N42</f>
+      <c r="L42" s="45">
+        <f t="shared" si="1"/>
         <v>8.125</v>
       </c>
-      <c r="M42" s="72">
-        <f>(U42+W42)/2</f>
-        <v>10</v>
-      </c>
-      <c r="N42" s="72">
+      <c r="M42" s="59">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="N42" s="59">
         <v>7.5</v>
       </c>
-      <c r="O42" s="72">
-        <f>O41</f>
+      <c r="O42" s="59">
+        <f t="shared" si="7"/>
         <v>6.5</v>
       </c>
-      <c r="P42" s="73"/>
-      <c r="Q42" s="59"/>
-      <c r="R42" s="59"/>
-      <c r="S42" s="59"/>
-      <c r="T42" s="62"/>
+      <c r="P42" s="60"/>
+      <c r="Q42" s="48"/>
+      <c r="R42" s="48"/>
+      <c r="S42" s="48"/>
+      <c r="T42" s="50"/>
       <c r="U42" s="22">
         <v>10</v>
       </c>
@@ -6142,17 +6131,17 @@
       <c r="X42" s="33"/>
     </row>
     <row r="43" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="I43" s="53" t="s">
+      <c r="I43" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="K43" s="53"/>
+      <c r="K43" s="43"/>
       <c r="L43" s="6"/>
     </row>
     <row r="44" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="I44" s="53" t="s">
+      <c r="I44" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="K44" s="53"/>
+      <c r="K44" s="43"/>
       <c r="L44" s="6"/>
     </row>
   </sheetData>
@@ -6197,222 +6186,345 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BE7A4D6-E7E7-49D9-867D-73D4DD749CB9}">
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="47.7109375" style="65" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="71"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="64" t="s">
+        <v>249</v>
+      </c>
+      <c r="B1" s="70" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="65" t="s">
+        <v>236</v>
+      </c>
+      <c r="B2" s="43">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="65" t="s">
+        <v>237</v>
+      </c>
+      <c r="B3" s="43">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="65" t="s">
+        <v>238</v>
+      </c>
+      <c r="B4" s="43" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="65" t="s">
+        <v>239</v>
+      </c>
+      <c r="B5" s="43">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="65" t="s">
+        <v>240</v>
+      </c>
+      <c r="B6" s="43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="65" t="s">
+        <v>241</v>
+      </c>
+      <c r="B7" s="43">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="65" t="s">
+        <v>242</v>
+      </c>
+      <c r="B8" s="43" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="65" t="s">
+        <v>243</v>
+      </c>
+      <c r="B9" s="43">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="65" t="s">
+        <v>244</v>
+      </c>
+      <c r="B10" s="43" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="65" t="s">
+        <v>245</v>
+      </c>
+      <c r="B11" s="43" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="65" t="s">
+        <v>246</v>
+      </c>
+      <c r="B12" s="43">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="65" t="s">
+        <v>247</v>
+      </c>
+      <c r="B13" s="43">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="65" t="s">
+        <v>248</v>
+      </c>
+      <c r="B14" s="43">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A98778EE-FBFC-4E47-98AB-2B66B2949A66}">
   <dimension ref="A1:C22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="50.85546875" style="78" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="47.7109375" style="78" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="50.85546875" style="78" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="78"/>
+    <col min="1" max="1" width="50.85546875" style="65" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="25" style="68" customWidth="1"/>
+    <col min="3" max="3" width="11" style="68" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="65"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="64" t="s">
         <v>214</v>
       </c>
-      <c r="B1" s="77" t="s">
+      <c r="B1" s="69" t="s">
         <v>249</v>
       </c>
-      <c r="C1" s="77" t="s">
+      <c r="C1" s="69" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="78" t="s">
+      <c r="A2" s="65" t="s">
         <v>215</v>
       </c>
-      <c r="B2" s="78" t="s">
+      <c r="B2" s="68" t="s">
         <v>236</v>
       </c>
-      <c r="C2" s="78" t="s">
+      <c r="C2" s="68" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="78" t="s">
+      <c r="A3" s="65" t="s">
         <v>216</v>
       </c>
-      <c r="B3" s="78" t="s">
+      <c r="B3" s="68" t="s">
         <v>237</v>
       </c>
-      <c r="C3" s="78" t="s">
+      <c r="C3" s="68" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="78" t="s">
+      <c r="A4" s="65" t="s">
         <v>217</v>
       </c>
-      <c r="B4" s="78" t="s">
+      <c r="B4" s="68" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="78" t="s">
+      <c r="A5" s="65" t="s">
         <v>218</v>
       </c>
-      <c r="B5" s="78" t="s">
+      <c r="B5" s="68" t="s">
         <v>239</v>
       </c>
-      <c r="C5" s="78" t="s">
+      <c r="C5" s="68" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="78" t="s">
+      <c r="A6" s="65" t="s">
         <v>219</v>
       </c>
-      <c r="B6" s="78" t="s">
+      <c r="B6" s="68" t="s">
         <v>240</v>
       </c>
-      <c r="C6" s="78" t="s">
+      <c r="C6" s="68" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="78" t="s">
+      <c r="A7" s="65" t="s">
         <v>220</v>
       </c>
-      <c r="C7" s="78" t="s">
+      <c r="C7" s="68" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="74" t="s">
+      <c r="A8" s="61" t="s">
         <v>221</v>
       </c>
-      <c r="C8" s="74"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="78" t="s">
+      <c r="A9" s="65" t="s">
         <v>222</v>
       </c>
-      <c r="C9" s="78" t="s">
+      <c r="C9" s="68" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="78" t="s">
+      <c r="A10" s="65" t="s">
         <v>223</v>
       </c>
-      <c r="C10" s="78" t="s">
+      <c r="C10" s="68" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="78" t="s">
+      <c r="A11" s="65" t="s">
         <v>224</v>
       </c>
-      <c r="B11" s="78" t="s">
+      <c r="B11" s="68" t="s">
         <v>241</v>
       </c>
-      <c r="C11" s="78" t="s">
+      <c r="C11" s="68" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="78" t="s">
+      <c r="A12" s="65" t="s">
         <v>225</v>
       </c>
-      <c r="B12" s="78" t="s">
+      <c r="B12" s="68" t="s">
         <v>242</v>
       </c>
-      <c r="C12" s="78" t="s">
+      <c r="C12" s="68" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="74" t="s">
+      <c r="A13" s="61" t="s">
         <v>226</v>
       </c>
-      <c r="C13" s="74"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="78" t="s">
+      <c r="A14" s="65" t="s">
         <v>227</v>
       </c>
-      <c r="C14" s="78" t="s">
+      <c r="C14" s="68" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="78" t="s">
+      <c r="A15" s="65" t="s">
         <v>228</v>
       </c>
-      <c r="B15" s="78" t="s">
+      <c r="B15" s="68" t="s">
         <v>243</v>
       </c>
-      <c r="C15" s="78" t="s">
+      <c r="C15" s="68" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="16" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="74" t="s">
+      <c r="A16" s="61" t="s">
         <v>229</v>
       </c>
-      <c r="C16" s="74"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="78" t="s">
+      <c r="A17" s="65" t="s">
         <v>230</v>
       </c>
-      <c r="B17" s="78" t="s">
+      <c r="B17" s="68" t="s">
         <v>244</v>
       </c>
-      <c r="C17" s="78" t="s">
+      <c r="C17" s="68" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="78" t="s">
+      <c r="A18" s="65" t="s">
         <v>231</v>
       </c>
-      <c r="B18" s="78" t="s">
+      <c r="B18" s="68" t="s">
         <v>245</v>
       </c>
-      <c r="C18" s="78" t="s">
+      <c r="C18" s="68" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="78" t="s">
+      <c r="A19" s="65" t="s">
         <v>232</v>
       </c>
-      <c r="B19" s="78" t="s">
+      <c r="B19" s="68" t="s">
         <v>246</v>
       </c>
-      <c r="C19" s="78" t="s">
+      <c r="C19" s="68" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="78" t="s">
+      <c r="A20" s="65" t="s">
         <v>233</v>
       </c>
-      <c r="B20" s="78" t="s">
+      <c r="B20" s="68" t="s">
         <v>247</v>
       </c>
-      <c r="C20" s="78" t="s">
+      <c r="C20" s="68" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="78" t="s">
+      <c r="A21" s="65" t="s">
         <v>234</v>
       </c>
-      <c r="B21" s="78" t="s">
+      <c r="B21" s="68" t="s">
         <v>248</v>
       </c>
-      <c r="C21" s="78" t="s">
+      <c r="C21" s="68" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="78" t="s">
+      <c r="A22" s="65" t="s">
         <v>235</v>
       </c>
-      <c r="C22" s="78" t="s">
+      <c r="C22" s="68" t="s">
         <v>261</v>
       </c>
     </row>
